--- a/Digitised_Records_High_Frequency_2026_05_06.xlsx
+++ b/Digitised_Records_High_Frequency_2026_05_06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sotonac-my.sharepoint.com/personal/ck1g20_soton_ac_uk/Documents/Documents/PhD/20_Historical_record_catalogue/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{20516951-3379-4B2C-8F4C-42D953C85CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76B34816-E9FB-4566-B455-9518FCE8F722}"/>
+  <xr:revisionPtr revIDLastSave="195" documentId="8_{20516951-3379-4B2C-8F4C-42D953C85CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FE19517-C0A1-4ECB-8376-F68E8C1D79A1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8FB86131-9B33-41BE-BB40-45738662AB11}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="423">
   <si>
     <t>Location</t>
   </si>
@@ -86,9 +86,6 @@
     <t>Hourly</t>
   </si>
   <si>
-    <t>comparison of recent and historical tides and mean sea-levels off Ireland | Geophysical Journal International | Oxford Academic</t>
-  </si>
-  <si>
     <t>Ballycastle</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
     <t>Colombia</t>
   </si>
   <si>
-    <t>ESM13/4</t>
-  </si>
-  <si>
     <t>Tumaco</t>
   </si>
   <si>
@@ -263,9 +257,6 @@
     <t>01/01/1854-31/05/1854, 01/12/1877-31/12/1877</t>
   </si>
   <si>
-    <t>Storminess Variability along the California Coast: 1858–2000 in: Journal of Climate Volume 16 Issue 6 (2003)</t>
-  </si>
-  <si>
     <t>Presidio</t>
   </si>
   <si>
@@ -275,15 +266,9 @@
     <t>New Zealand</t>
   </si>
   <si>
-    <t>An updated analysis of long‐term sea level change in New Zealand - Hannah - 2004 - Geophysical Research Letters - Wiley Online Library</t>
-  </si>
-  <si>
     <t>Jardions du Roy</t>
   </si>
   <si>
-    <t>Brest sea level record: a time series construction back to the early eighteenth century | Ocean Dynamics</t>
-  </si>
-  <si>
     <t>Pointe de la Rose</t>
   </si>
   <si>
@@ -305,18 +290,12 @@
     <t>French Southern and Antartic Lands</t>
   </si>
   <si>
-    <t>The sea level at Port-aux-Français, Kerguelen Island, from 1949 to the present | Ocean Dynamics</t>
-  </si>
-  <si>
     <t>01/09/1962 - 14/03/1963, 15/08/1963 - 25/10/1972</t>
   </si>
   <si>
     <t>Honolulu</t>
   </si>
   <si>
-    <t>Tales of the Venerable Honolulu Tide Gauge in: Journal of Physical Oceanography Volume 36 Issue 6 (2006)</t>
-  </si>
-  <si>
     <t>Hilo</t>
   </si>
   <si>
@@ -335,9 +314,6 @@
     <t>NUNIEAU</t>
   </si>
   <si>
-    <t>Extreme sea levels in two northern Mediterranean areas</t>
-  </si>
-  <si>
     <t>Oceanographic Platform</t>
   </si>
   <si>
@@ -350,15 +326,9 @@
     <t>Grau-de-la-Dent</t>
   </si>
   <si>
-    <t>Sea surges in Camargue: Trends over the 20th century - ScienceDirect</t>
-  </si>
-  <si>
     <t>St Marys</t>
   </si>
   <si>
-    <t>Mean sea level trends around the English Channel over the 20th century and their wider context - ScienceDirect</t>
-  </si>
-  <si>
     <t>Devonport</t>
   </si>
   <si>
@@ -377,27 +347,18 @@
     <t>Saint Paul Island</t>
   </si>
   <si>
-    <t>Sea level at Saint Paul Island, southern Indian Ocean, from 1874 to the present - Testut - 2010 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
-  </si>
-  <si>
     <t>Port Louis</t>
   </si>
   <si>
     <t>01/01/1842 - 09/05/1842, 16/12/1842-31/12/1842</t>
   </si>
   <si>
-    <t>Long‐term and recent changes in sea level in the Falkland Islands - Woodworth - 2010 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
-  </si>
-  <si>
     <t>Macquarie Island</t>
   </si>
   <si>
     <t xml:space="preserve">01/01/1912 - 31/07/1912, 01/06/1913-31/12/1913 </t>
   </si>
   <si>
-    <t>Twentieth century constraints on sea level change and earthquake deformation at Macquarie Island | Geophysical Journal International | Oxford Academic</t>
-  </si>
-  <si>
     <t>Cadiz</t>
   </si>
   <si>
@@ -407,18 +368,12 @@
     <t>Daily Average</t>
   </si>
   <si>
-    <t>The long sea level record at Cadiz (southern Spain) from 1880 to 2009 - Marcos - 2011 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
-  </si>
-  <si>
     <t>Ascension Island</t>
   </si>
   <si>
     <t>01/01/1955 - 22/02/1955, 23/03/1955-31/12/1955</t>
   </si>
   <si>
-    <t>Sea level changes at Ascension Island in the last half century: African Journal of Marine Science: Vol 34, No 3</t>
-  </si>
-  <si>
     <t>Nice</t>
   </si>
   <si>
@@ -428,18 +383,12 @@
     <t>1-minute</t>
   </si>
   <si>
-    <t>Refined numerical modeling of the 1979 tsunami in Nice (French Riviera): Comparison with coastal data - Labbé - 2012 - Journal of Geophysical Research: Earth Surface - Wiley Online Library</t>
-  </si>
-  <si>
     <t>Villefranche</t>
   </si>
   <si>
     <t>Santa Cruz harbour (Southern Pier)</t>
   </si>
   <si>
-    <t>Sea level changes at Tenerife Island (NE Tropical Atlantic) since 1927 - Marcos - 2013 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
-  </si>
-  <si>
     <t>Santa Cruz harbour (Northern Pier)</t>
   </si>
   <si>
@@ -458,9 +407,6 @@
     <t>La Rochelle, Vieux Port</t>
   </si>
   <si>
-    <t>Reconstruction of a two-century long sea level record for the Pertuis d’Antioche (France) - ScienceDirect</t>
-  </si>
-  <si>
     <t>La Pallice</t>
   </si>
   <si>
@@ -482,15 +428,9 @@
     <t>Germany</t>
   </si>
   <si>
-    <t>Characteristics of intra-, inter-annual and decadal sea-level variability and the role of meteorological forcing: the long record of Cuxhaven | Ocean Dynamics</t>
-  </si>
-  <si>
     <t>Yamba</t>
   </si>
   <si>
-    <t>Nineteenth Century North American and Pacific Tidal Data: Lost or Just Forgotten? | Journal of Coastal Research</t>
-  </si>
-  <si>
     <t>Hobart</t>
   </si>
   <si>
@@ -533,9 +473,6 @@
     <t>Marigram</t>
   </si>
   <si>
-    <t>Increasing storm tides in New York Harbor, 1844–2013 - Talke - 2014 - Geophysical Research Letters - Wiley Online Library</t>
-  </si>
-  <si>
     <t>Hamilton ferry dock in Brooklyn</t>
   </si>
   <si>
@@ -548,9 +485,6 @@
     <t>Chazallon</t>
   </si>
   <si>
-    <t>Rescue of the historical sea level record of Marseille (France) from 1885 to 1988 and its extension back to 1849–1851 | Journal of Geodesy</t>
-  </si>
-  <si>
     <t>Totalisateur</t>
   </si>
   <si>
@@ -569,9 +503,6 @@
     <t>Continuous</t>
   </si>
   <si>
-    <t>(PDF) Maintaining legacy data: Saving Belfast Harbour (UK) tide-gauge data (1901–2010)</t>
-  </si>
-  <si>
     <t>Tide gauge 2 (Belfast)</t>
   </si>
   <si>
@@ -587,9 +518,6 @@
     <t>Hourly, 15min</t>
   </si>
   <si>
-    <t>27-2016 Rapport_Final_Reconstruction_serie_SaintNazaire</t>
-  </si>
-  <si>
     <t xml:space="preserve">NUNIEAU </t>
   </si>
   <si>
@@ -599,9 +527,6 @@
     <t>Southport</t>
   </si>
   <si>
-    <t>The effect of channel deepening on tides and storm surge: A case study of Wilmington, NC - Familkhalili - 2016 - Geophysical Research Letters - Wiley Online Library</t>
-  </si>
-  <si>
     <t>Wilmington</t>
   </si>
   <si>
@@ -611,9 +536,6 @@
     <t>HLW, Hourly</t>
   </si>
   <si>
-    <t>Archival Water-Level Measurements: Recovering Historical Data to Help Design for the Future</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pulpit Harbour </t>
   </si>
   <si>
@@ -740,9 +662,6 @@
     <t>Boston tide gauge</t>
   </si>
   <si>
-    <t>Relative Sea Level, Tides, and Extreme Water Levels in Boston Harbor From 1825 to 2018 - Talke - 2018 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
-  </si>
-  <si>
     <t>Baldwin data</t>
   </si>
   <si>
@@ -758,15 +677,9 @@
     <t>Albany</t>
   </si>
   <si>
-    <t>Bigger Tides, Less Flooding: Effects of Dredging on Barotropic Dynamics in a Highly Modified Estuary - Ralston - 2019 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
-  </si>
-  <si>
     <t>Port Elizabeth</t>
   </si>
   <si>
-    <t>Impact of Channel Deepening on Tidal and Gravitational Circulation in a Highly Engineered Estuarine Basin | Estuaries and Coasts</t>
-  </si>
-  <si>
     <t>Port Newark</t>
   </si>
   <si>
@@ -785,9 +698,6 @@
     <t>Tide gauge 1 (Canale Candio)</t>
   </si>
   <si>
-    <t>Rescue of the 1873–1922 high and low waters of the Porto Corsini/Marina di Ravenna (northern Adriatic, Italy) tide gauge | Journal of Geodesy</t>
-  </si>
-  <si>
     <t>Tide gauge 2 (Canale Candio)</t>
   </si>
   <si>
@@ -797,9 +707,6 @@
     <t>HLW, 30min</t>
   </si>
   <si>
-    <t>Nineteenth‐Century Tides in the Gulf of Maine and Implications for Secular Trends - Ray - 2019 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
-  </si>
-  <si>
     <t>01/01/1864-31/07/1864, 01/11/1866-31/12/1866</t>
   </si>
   <si>
@@ -824,9 +731,6 @@
     <t>6min, hourly</t>
   </si>
   <si>
-    <t>Sea Level, Tidal, and River Flow Trends in the Lower Columbia River Estuary, 1853–present - Talke - 2020 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
-  </si>
-  <si>
     <t>Astoria tongue point</t>
   </si>
   <si>
@@ -842,9 +746,6 @@
     <t>Dunkerque</t>
   </si>
   <si>
-    <t>Influence des modifications morphologiques de l'avant-côte sur l'hydrodynamisme et l'évolution du littoral des Hauts-de-France depuis le XIXe siècle - TEL - Thèses en ligne</t>
-  </si>
-  <si>
     <t>Calais</t>
   </si>
   <si>
@@ -857,9 +758,6 @@
     <t>6hr</t>
   </si>
   <si>
-    <t>Historical tide gauge sea‐level observations in Alicante and Santander (Spain) since the 19th century - Marcos - 2021 - Geoscience Data Journal - Wiley Online Library</t>
-  </si>
-  <si>
     <t>Adie (Outer harbour)</t>
   </si>
   <si>
@@ -893,15 +791,9 @@
     <t>Continuous, weekly max</t>
   </si>
   <si>
-    <t>Digitisation and Analysis of Poole Harbour Tide Gauge Record</t>
-  </si>
-  <si>
     <t>Mayport</t>
   </si>
   <si>
-    <t>The Influence of Channel Deepening on Tides, River Discharge Effects, and Storm Surge - Talke - 2021 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
-  </si>
-  <si>
     <t>Acosta Bridge</t>
   </si>
   <si>
@@ -914,18 +806,12 @@
     <t>Passage West (Cork)</t>
   </si>
   <si>
-    <t>OS - Mean sea level and tidal change in Ireland since 1842: a case study of Cork</t>
-  </si>
-  <si>
     <t>Cobh</t>
   </si>
   <si>
     <t>Walton-on-Naze</t>
   </si>
   <si>
-    <t>Digitising historical sea level records in the Thames Estuary, UK - ProQuest</t>
-  </si>
-  <si>
     <t>Margate Harbour</t>
   </si>
   <si>
@@ -965,36 +851,21 @@
     <t>Hourly, 5min</t>
   </si>
   <si>
-    <t>Extension of a high temporal resolution sea level time series at Socoa (Saint-Jean-de-Luz, France) back to 1875</t>
-  </si>
-  <si>
     <t>Quai Nord</t>
   </si>
   <si>
     <t>Ivory Coast</t>
   </si>
   <si>
-    <t>Evolutive Trend of Water Level in the Ebrie Lagoon by Reconstitution of the Tide Gauge Time Series in Front of the Abidjan Coastline (Côte d’Ivoire)</t>
-  </si>
-  <si>
     <t>Williamstown</t>
   </si>
   <si>
-    <t>Digitizing the Williamstown, Australia Tide‐Gauge Record Back to 1872: Insights Into Changing Extremes - McInnes - 2024 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
-  </si>
-  <si>
     <t>Dún Laoghaire Harbour</t>
   </si>
   <si>
-    <t>The accurate digitization of historical sea level records - McLoughlin - 2024 - Geoscience Data Journal - Wiley Online Library</t>
-  </si>
-  <si>
     <t>Sacramento River, I Street</t>
   </si>
   <si>
-    <t>Recovery of Daily Water Levels in the Sacramento‐San Joaquin Delta, 1915–2023 - Lee - 2025 - Geoscience Data Journal - Wiley Online Library</t>
-  </si>
-  <si>
     <t>Sacramento River, Snodgrass</t>
   </si>
   <si>
@@ -1073,9 +944,6 @@
     <t>15min</t>
   </si>
   <si>
-    <t>UK Tides — Zooniverse</t>
-  </si>
-  <si>
     <t>Hilbre Island</t>
   </si>
   <si>
@@ -1107,9 +975,6 @@
   </si>
   <si>
     <t>Ledger and Digital</t>
-  </si>
-  <si>
-    <t>Extension of a high temporal resolution sea level time series at Socoa (Saint-Jean-de-Luz, France) back to 1876</t>
   </si>
   <si>
     <t>Plot Digitizer</t>
@@ -1307,9 +1172,6 @@
     <t>01/01/1900-27/03/1900, 13/07/1900-31/12/1900</t>
   </si>
   <si>
-    <t>HGSS - Three historic tide gauge records from Svalbard</t>
-  </si>
-  <si>
     <t>01/01/1872-19/10/1872, 27/11/1872-17/02/1893, 25/04/1873-31/12/1873</t>
   </si>
   <si>
@@ -1332,6 +1194,141 @@
   </si>
   <si>
     <t>UnGraph</t>
+  </si>
+  <si>
+    <t>https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf</t>
+  </si>
+  <si>
+    <t>https://journals.ametsoc.org/view/journals/clim/16/6/1520-0442_2003_016_0982_svatcc_2.0.co_2.xml</t>
+  </si>
+  <si>
+    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2003GL019166</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/gji/article/71/3/809/656230?login=true</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/s10236-005-0056-8</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/s10236-005-0044-z</t>
+  </si>
+  <si>
+    <t>https://journals.ametsoc.org/view/journals/phoc/36/6/jpo2876.1.xml</t>
+  </si>
+  <si>
+    <t>https://journals.openedition.org/mediterranee/170#tocto1n3</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0278434306003888#sec2</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0278434309002313</t>
+  </si>
+  <si>
+    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2010JC006404</t>
+  </si>
+  <si>
+    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2010JC006113</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/gji/article/182/2/781/571033</t>
+  </si>
+  <si>
+    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2011JC007558</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/doi/abs/10.2989/1814232X.2012.689623?casa_token=zBny8ik3tAMAAAAA:D-WLZrlhXskUGl1Xag8khGwd83rNrPI2GZ94RlKOsCvfW4t4DDubKDq8PhmhPgZCerNLRIoGbCBZ</t>
+  </si>
+  <si>
+    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2011JF001964</t>
+  </si>
+  <si>
+    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/jgrc.20377</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0278434313001283#s0010</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/s10236-013-0598-0</t>
+  </si>
+  <si>
+    <t>https://www.researchgate.net/publication/261063515_Nineteenth_Century_North_American_and_Pacific_Tidal_Data_Lost_or_Just_Forgotten</t>
+  </si>
+  <si>
+    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/2014GL059574</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/s00190-014-0728-6</t>
+  </si>
+  <si>
+    <t>https://www.researchgate.net/publication/273705568_Maintaining_legacy_data_Saving_Belfast_Harbour_UK_tide-gauge_data_1901-2010</t>
+  </si>
+  <si>
+    <t>https://refmar.shom.fr/sites/default/files/2024-07/Reconstruction%20serie%20maregraphique%20Saint-Nazaire%20par%20Yann%20Ferret%202016.pdf</t>
+  </si>
+  <si>
+    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/2016GL069494</t>
+  </si>
+  <si>
+    <t>https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac</t>
+  </si>
+  <si>
+    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2017JC013645</t>
+  </si>
+  <si>
+    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2018JC014313</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/s12237-018-0379-6</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/s00190-019-01238-w#Sec2</t>
+  </si>
+  <si>
+    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2019JC015277</t>
+  </si>
+  <si>
+    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2019JC015656</t>
+  </si>
+  <si>
+    <t>https://theses.hal.science/tel-02899411/</t>
+  </si>
+  <si>
+    <t>https://rmets.onlinelibrary.wiley.com/doi/full/10.1002/gdj3.112</t>
+  </si>
+  <si>
+    <t>https://southerncoastalgroup-scopac.org.uk/wp-content/uploads/2022/01/Digitisation-and-Analysis-of-Poole-Harbour-Tide-Gauge-Record-September-2021.pdf</t>
+  </si>
+  <si>
+    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2020JC016328</t>
+  </si>
+  <si>
+    <t>https://os.copernicus.org/articles/17/1623/2021/#section2</t>
+  </si>
+  <si>
+    <t>https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals</t>
+  </si>
+  <si>
+    <t>https://hal.science/hal-04555208v1/file/Khan2023.pdf</t>
+  </si>
+  <si>
+    <t>https://www.scirp.org/journal/paperinformation?paperid=128406</t>
+  </si>
+  <si>
+    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2024JC020908</t>
+  </si>
+  <si>
+    <t>https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.256</t>
+  </si>
+  <si>
+    <t>https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018</t>
+  </si>
+  <si>
+    <t>https://hgss.copernicus.org/articles/17/1/2026/</t>
+  </si>
+  <si>
+    <t>https://www.zooniverse.org/projects/psmsl/uk-tides</t>
   </si>
 </sst>
 </file>
@@ -1488,7 +1485,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1532,6 +1529,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1909,13 +1907,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>359</v>
+        <v>314</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>360</v>
+        <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>7</v>
@@ -1924,7 +1922,7 @@
         <v>8</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>363</v>
+        <v>318</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>10</v>
@@ -1961,7 +1959,7 @@
         <v>136.16666666666666</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>9</v>
@@ -1970,12 +1968,12 @@
         <v>15</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>16</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>13</v>
@@ -1997,14 +1995,14 @@
         <v>1.863636363636374</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I3" s="4">
         <f>0.5+137-(4/11)</f>
         <v>137.13636363636363</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>9</v>
@@ -2013,12 +2011,12 @@
         <v>15</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>16</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>13</v>
@@ -2040,14 +2038,14 @@
         <v>1.3333333333333428</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I4" s="4">
         <f>0.5+0.5+135- (4/12)</f>
         <v>135.66666666666666</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>9</v>
@@ -2056,15 +2054,15 @@
         <v>15</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>16</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="C5" s="4">
         <v>10.421473000000001</v>
@@ -2089,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>9</v>
@@ -2098,15 +2096,15 @@
         <v>15</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="4">
         <v>1.811604</v>
@@ -2131,7 +2129,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>9</v>
@@ -2140,15 +2138,15 @@
         <v>15</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="4">
         <v>3.8885350000000001</v>
@@ -2173,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>9</v>
@@ -2182,15 +2180,15 @@
         <v>15</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C8" s="4">
         <v>13.584844</v>
@@ -2209,14 +2207,14 @@
         <v>15</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I8" s="4">
         <f>1+(F8-E8)-15</f>
         <v>14</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>9</v>
@@ -2225,15 +2223,15 @@
         <v>15</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C9" s="4">
         <v>8.2675660000000004</v>
@@ -2258,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>9</v>
@@ -2267,15 +2265,15 @@
         <v>15</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C10" s="4">
         <v>7.3388530000000003</v>
@@ -2300,7 +2298,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>9</v>
@@ -2309,15 +2307,15 @@
         <v>15</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" s="4">
         <v>2.0270860000000002</v>
@@ -2342,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>9</v>
@@ -2351,15 +2349,15 @@
         <v>15</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="4">
         <v>-1.2794319999999999</v>
@@ -2384,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>9</v>
@@ -2393,15 +2391,15 @@
         <v>15</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13" s="4">
         <v>-0.52425100000000002</v>
@@ -2426,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>9</v>
@@ -2435,15 +2433,15 @@
         <v>15</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>11</v>
@@ -2468,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>9</v>
@@ -2477,15 +2475,15 @@
         <v>15</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>11</v>
@@ -2510,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>9</v>
@@ -2519,15 +2517,15 @@
         <v>15</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" s="4">
         <v>16.226343</v>
@@ -2552,7 +2550,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>9</v>
@@ -2561,15 +2559,15 @@
         <v>15</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C17" s="4">
         <v>-1.453643</v>
@@ -2594,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>9</v>
@@ -2603,15 +2601,15 @@
         <v>15</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C18" s="4">
         <v>-3.7184849999999998</v>
@@ -2636,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>9</v>
@@ -2645,15 +2643,15 @@
         <v>15</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" s="4">
         <v>-8.0470780000000008</v>
@@ -2678,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>9</v>
@@ -2687,15 +2685,15 @@
         <v>15</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C20" s="4">
         <v>-12.972312000000001</v>
@@ -2720,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>9</v>
@@ -2729,15 +2727,15 @@
         <v>15</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C21" s="4">
         <v>-15.683204</v>
@@ -2762,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>9</v>
@@ -2771,15 +2769,15 @@
         <v>15</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C22" s="4">
         <v>-22.902732</v>
@@ -2804,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>9</v>
@@ -2813,15 +2811,15 @@
         <v>15</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C23" s="4">
         <v>15.828041000000001</v>
@@ -2846,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>9</v>
@@ -2855,15 +2853,15 @@
         <v>15</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C24" s="4">
         <v>16.004376000000001</v>
@@ -2888,7 +2886,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>9</v>
@@ -2897,15 +2895,15 @@
         <v>15</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C25" s="4">
         <v>17.935072999999999</v>
@@ -2930,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>9</v>
@@ -2939,15 +2937,15 @@
         <v>15</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C26" s="4">
         <v>19.919588000000001</v>
@@ -2972,7 +2970,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>9</v>
@@ -2981,15 +2979,15 @@
         <v>15</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="4">
         <v>18.338353999999999</v>
@@ -3014,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>9</v>
@@ -3023,15 +3021,15 @@
         <v>15</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C28" s="4">
         <v>32.290323000000001</v>
@@ -3056,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>9</v>
@@ -3065,15 +3063,15 @@
         <v>15</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C29" s="4">
         <v>13.095783000000001</v>
@@ -3098,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>9</v>
@@ -3107,15 +3105,15 @@
         <v>15</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C30" s="4">
         <v>5.8875739999999999</v>
@@ -3140,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>9</v>
@@ -3149,15 +3147,15 @@
         <v>15</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C31" s="4">
         <v>13.338308</v>
@@ -3182,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>9</v>
@@ -3191,15 +3189,15 @@
         <v>15</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C32" s="4">
         <v>12.477584999999999</v>
@@ -3224,7 +3222,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>9</v>
@@ -3233,15 +3231,15 @@
         <v>15</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C33" s="4">
         <v>9.2578759999999996</v>
@@ -3266,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>9</v>
@@ -3275,15 +3273,15 @@
         <v>15</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C34" s="4">
         <v>10.186114</v>
@@ -3308,7 +3306,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>9</v>
@@ -3317,15 +3315,15 @@
         <v>15</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C35" s="4">
         <v>10.64817</v>
@@ -3350,7 +3348,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>9</v>
@@ -3359,15 +3357,15 @@
         <v>15</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>28</v>
+        <v>378</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C36" s="4">
         <v>37.810837999999997</v>
@@ -3386,30 +3384,30 @@
         <v>23.5</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I36" s="4">
         <v>0.5</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M36" s="6" t="s">
-        <v>75</v>
+      <c r="M36" s="29" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C37" s="4">
         <v>37.805551999999999</v>
@@ -3428,30 +3426,30 @@
         <v>103.5</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>364</v>
+        <v>319</v>
       </c>
       <c r="I37" s="4">
         <v>0.5</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L37" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M37" s="6" t="s">
-        <v>75</v>
+      <c r="M37" s="29" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C38" s="7">
         <v>-41.28434</v>
@@ -3476,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>9</v>
@@ -3485,15 +3483,15 @@
         <v>15</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>79</v>
+        <v>380</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>11</v>
@@ -3519,24 +3517,24 @@
         <v>0.97809719370294324</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K39" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="M39" s="5" t="s">
-        <v>81</v>
+        <v>21</v>
+      </c>
+      <c r="M39" s="29" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C40" s="4">
         <v>48.380504000000002</v>
@@ -3555,30 +3553,30 @@
         <v>7</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I40" s="4">
         <v>18</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="M40" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="M40" s="29" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C41" s="4">
         <v>48.386029999999998</v>
@@ -3597,31 +3595,31 @@
         <v>44</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I41" s="4">
         <f>18+1+13</f>
         <v>32</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="M41" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="M41" s="29" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>365</v>
+        <v>320</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C42" s="4">
         <v>48.382953000000001</v>
@@ -3640,13 +3638,13 @@
         <v>119</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="I42" s="4">
         <v>44</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>9</v>
@@ -3654,16 +3652,16 @@
       <c r="L42" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M42" s="5" t="s">
-        <v>81</v>
+      <c r="M42" s="29" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>365</v>
+        <v>320</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C43" s="4">
         <v>48.382953000000001</v>
@@ -3688,24 +3686,24 @@
         <v>0</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="M43" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="M43" s="29" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>366</v>
+        <v>321</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C44" s="4">
         <v>-49.352224999999997</v>
@@ -3724,14 +3722,14 @@
         <v>1.2634446691001457</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I44" s="4">
         <f>((31+30+31+31+31+28+14)/365.2)+9+((17+31+25)/365.25)</f>
         <v>9.7365553308998543</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>9</v>
@@ -3740,15 +3738,15 @@
         <v>15</v>
       </c>
       <c r="M44" s="5" t="s">
-        <v>89</v>
+        <v>382</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C45" s="4">
         <v>21.312847000000001</v>
@@ -3767,30 +3765,30 @@
         <v>83</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I45" s="4">
         <v>13</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M45" s="5" t="s">
-        <v>92</v>
+        <v>384</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C46" s="4">
         <v>19.724398000000001</v>
@@ -3815,24 +3813,24 @@
         <v>0</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>92</v>
+        <v>384</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="13" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C47" s="7">
         <v>45.65</v>
@@ -3856,24 +3854,24 @@
         <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L47" s="8" t="s">
         <v>15</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>99</v>
+        <v>385</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" s="13" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C48" s="7">
         <v>45.3</v>
@@ -3891,30 +3889,30 @@
         <v>27.2</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I48" s="4">
         <v>4.8</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L48" s="8" t="s">
         <v>15</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>99</v>
+        <v>385</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" s="13" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C49" s="7">
         <v>45.42</v>
@@ -3932,30 +3930,30 @@
         <v>36.5</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I49" s="4">
         <v>1.48</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L49" s="8" t="s">
         <v>15</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>99</v>
+        <v>385</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" s="13" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C50" s="7">
         <v>45.43</v>
@@ -3973,30 +3971,30 @@
         <v>64.5</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I50" s="4">
         <v>1.51</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L50" s="8" t="s">
         <v>15</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>99</v>
+        <v>385</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" s="13" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C51" s="7">
         <v>42.52</v>
@@ -4014,30 +4012,30 @@
         <v>13.7</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I51" s="4">
         <v>1.06</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L51" s="8" t="s">
         <v>15</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>99</v>
+        <v>385</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" s="13" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C52" s="7">
         <v>43.4</v>
@@ -4055,30 +4053,30 @@
         <v>13.6</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I52" s="4">
         <v>0.35</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L52" s="8" t="s">
         <v>15</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>99</v>
+        <v>385</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="13" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C53" s="7">
         <v>43.36</v>
@@ -4096,30 +4094,30 @@
         <v>14</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I53" s="4">
         <v>3</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L53" s="8" t="s">
         <v>15</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>104</v>
+        <v>386</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C54" s="4">
         <v>49.911884999999998</v>
@@ -4144,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>9</v>
@@ -4153,15 +4151,15 @@
         <v>15</v>
       </c>
       <c r="M54" s="5" t="s">
-        <v>106</v>
+        <v>387</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C55" s="4">
         <v>50.371918999999998</v>
@@ -4186,7 +4184,7 @@
         <v>1</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K55" s="3" t="s">
         <v>9</v>
@@ -4195,15 +4193,15 @@
         <v>15</v>
       </c>
       <c r="M55" s="5" t="s">
-        <v>106</v>
+        <v>387</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C56" s="4">
         <v>50.599704000000003</v>
@@ -4228,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>9</v>
@@ -4237,15 +4235,15 @@
         <v>15</v>
       </c>
       <c r="M56" s="5" t="s">
-        <v>106</v>
+        <v>387</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C57" s="4">
         <v>50.895299999999999</v>
@@ -4264,14 +4262,14 @@
         <v>37</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="I57" s="4">
         <f>16+2</f>
         <v>18</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>9</v>
@@ -4280,15 +4278,15 @@
         <v>15</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>106</v>
+        <v>387</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C58" s="4">
         <v>50.800559999999997</v>
@@ -4313,7 +4311,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>9</v>
@@ -4322,15 +4320,15 @@
         <v>15</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>106</v>
+        <v>387</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C59" s="4">
         <v>-38.714312999999997</v>
@@ -4355,24 +4353,24 @@
         <v>0</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>113</v>
+        <v>388</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C60" s="4">
         <v>-51.534190000000002</v>
@@ -4391,31 +4389,31 @@
         <v>0.60301163586584527</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="I60" s="4">
         <f>((31+28+31+30+9+16)/365.25)</f>
         <v>0.39698836413415467</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M60" s="5" t="s">
-        <v>116</v>
+        <v>389</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C61" s="4">
         <v>-54.499370999999996</v>
@@ -4434,31 +4432,31 @@
         <v>1.375</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="I61" s="4">
         <f>5/8</f>
         <v>0.625</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>119</v>
+        <v>390</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C62" s="4">
         <v>36.533127999999998</v>
@@ -4483,24 +4481,24 @@
         <v>0</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="M62" s="5" t="s">
-        <v>123</v>
+        <v>391</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C63" s="4">
         <v>-7.8944989999999997</v>
@@ -4519,14 +4517,14 @@
         <v>8.0082135523613984E-2</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="I63" s="4">
         <f>((31+22+8+30+31+30+31+31+30+31+30+31)/365.25)</f>
         <v>0.91991786447638602</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K63" s="3" t="s">
         <v>9</v>
@@ -4535,15 +4533,15 @@
         <v>15</v>
       </c>
       <c r="M63" s="5" t="s">
-        <v>126</v>
+        <v>392</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C64" s="4">
         <v>43.693210000000001</v>
@@ -4562,31 +4560,31 @@
         <v>2.739726027397249E-3</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="I64" s="4">
         <f>364/365</f>
         <v>0.99726027397260275</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>130</v>
+        <v>393</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C65" s="4">
         <v>43.703366000000003</v>
@@ -4605,31 +4603,31 @@
         <v>2.739726027397249E-3</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="I65" s="4">
         <f>364/365</f>
         <v>0.99726027397260275</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>130</v>
+        <v>393</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C66" s="4">
         <v>28.472135000000002</v>
@@ -4654,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>9</v>
@@ -4663,15 +4661,15 @@
         <v>15</v>
       </c>
       <c r="M66" s="5" t="s">
-        <v>133</v>
+        <v>394</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C67" s="4">
         <v>28.477979000000001</v>
@@ -4696,7 +4694,7 @@
         <v>1</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K67" s="3" t="s">
         <v>9</v>
@@ -4705,15 +4703,15 @@
         <v>15</v>
       </c>
       <c r="M67" s="5" t="s">
-        <v>133</v>
+        <v>394</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C68" s="4">
         <v>28.472135000000002</v>
@@ -4738,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K68" s="3" t="s">
         <v>9</v>
@@ -4747,15 +4745,15 @@
         <v>15</v>
       </c>
       <c r="M68" s="5" t="s">
-        <v>133</v>
+        <v>394</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="27" t="s">
-        <v>368</v>
+        <v>323</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="C69" s="4">
         <v>41.186017999999997</v>
@@ -4774,30 +4772,30 @@
         <v>87</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="I69" s="4">
         <v>34</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>422</v>
+        <v>376</v>
       </c>
       <c r="L69" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M69" s="11" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="27" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="B70" s="27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C70" s="4">
         <v>46.155740000000002</v>
@@ -4816,13 +4814,13 @@
         <v>30</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>369</v>
+        <v>324</v>
       </c>
       <c r="I70" s="4">
         <v>39</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>355</v>
+        <v>311</v>
       </c>
       <c r="K70" s="3" t="s">
         <v>9</v>
@@ -4831,15 +4829,15 @@
         <v>15</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>140</v>
+        <v>395</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="27" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B71" s="27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C71" s="4">
         <v>46.158031000000001</v>
@@ -4858,14 +4856,14 @@
         <v>24</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>370</v>
+        <v>325</v>
       </c>
       <c r="I71" s="4">
         <f>48+22+14</f>
         <v>84</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>355</v>
+        <v>311</v>
       </c>
       <c r="K71" s="3" t="s">
         <v>9</v>
@@ -4874,15 +4872,15 @@
         <v>15</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>140</v>
+        <v>395</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="27" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C72" s="4">
         <v>46.007249999999999</v>
@@ -4901,14 +4899,14 @@
         <v>3</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="I72" s="4">
         <f>148</f>
         <v>148</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>355</v>
+        <v>311</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>9</v>
@@ -4917,15 +4915,15 @@
         <v>15</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>140</v>
+        <v>395</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="27" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B73" s="27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C73" s="4">
         <v>46.003768000000001</v>
@@ -4950,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K73" s="3" t="s">
         <v>9</v>
@@ -4959,15 +4957,15 @@
         <v>15</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>140</v>
+        <v>395</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="27" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="B74" s="27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C74" s="4">
         <v>45.999690999999999</v>
@@ -4992,7 +4990,7 @@
         <v>0</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K74" s="3" t="s">
         <v>9</v>
@@ -5001,15 +4999,15 @@
         <v>15</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>140</v>
+        <v>395</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="27" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="B75" s="27" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="C75" s="4">
         <v>53.890380999999998</v>
@@ -5034,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K75" s="3" t="s">
         <v>9</v>
@@ -5043,15 +5041,15 @@
         <v>15</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>148</v>
+        <v>396</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="27" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="B76" s="27" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="C76" s="4">
         <v>53.890380999999998</v>
@@ -5076,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>9</v>
@@ -5085,15 +5083,15 @@
         <v>15</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>148</v>
+        <v>396</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="27" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="B77" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C77" s="4">
         <v>-29.433214</v>
@@ -5118,24 +5116,24 @@
         <v>0</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L77" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M77" s="5" t="s">
-        <v>150</v>
+        <v>397</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="27" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="B78" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C78" s="4">
         <v>-42.884596000000002</v>
@@ -5160,24 +5158,24 @@
         <v>0</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K78" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L78" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M78" s="5" t="s">
-        <v>150</v>
+        <v>397</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="27" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="B79" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C79" s="4">
         <v>-28.869309000000001</v>
@@ -5202,24 +5200,24 @@
         <v>0</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K79" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L79" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M79" s="5" t="s">
-        <v>150</v>
+        <v>397</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="27" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="B80" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C80" s="4">
         <v>-27.380528999999999</v>
@@ -5244,24 +5242,24 @@
         <v>0</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K80" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L80" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M80" s="5" t="s">
-        <v>150</v>
+        <v>397</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="27" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="B81" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C81" s="4">
         <v>-16.921716</v>
@@ -5280,30 +5278,30 @@
         <v>45</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="I81" s="4">
         <v>9</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L81" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M81" s="5" t="s">
-        <v>150</v>
+        <v>397</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="27" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="B82" s="27" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C82" s="4">
         <v>-41.746557000000003</v>
@@ -5328,24 +5326,24 @@
         <v>0</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K82" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L82" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M82" s="5" t="s">
-        <v>150</v>
+        <v>397</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="27" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="B83" s="27" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C83" s="4">
         <v>-43.609394000000002</v>
@@ -5370,24 +5368,24 @@
         <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K83" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M83" s="5" t="s">
-        <v>150</v>
+        <v>397</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="27" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="B84" s="27" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C84" s="7">
         <v>38.296666999999999</v>
@@ -5412,24 +5410,24 @@
         <v>0</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L84" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M84" s="5" t="s">
-        <v>150</v>
+        <v>397</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="27" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="B85" s="27" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C85" s="4">
         <v>35.646303000000003</v>
@@ -5454,24 +5452,24 @@
         <v>0</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L85" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M85" s="5" t="s">
-        <v>150</v>
+        <v>397</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="27" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B86" s="27" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C86" s="4">
         <v>35.456859000000001</v>
@@ -5496,24 +5494,24 @@
         <v>0</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K86" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L86" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M86" s="5" t="s">
-        <v>150</v>
+        <v>397</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="27" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="B87" s="27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C87" s="4">
         <v>47.600962000000003</v>
@@ -5532,30 +5530,30 @@
         <v>113</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>372</v>
+        <v>327</v>
       </c>
       <c r="I87" s="4">
         <v>2</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K87" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L87" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M87" s="5" t="s">
-        <v>150</v>
+        <v>397</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="27" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="B88" s="27" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C88" s="4">
         <v>8.9181819999999998</v>
@@ -5580,24 +5578,24 @@
         <v>0</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K88" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L88" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M88" s="5" t="s">
-        <v>150</v>
+        <v>397</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C89" s="4">
         <v>40.691065000000002</v>
@@ -5616,30 +5614,30 @@
         <v>29</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>373</v>
+        <v>328</v>
       </c>
       <c r="I89" s="4">
         <v>5</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>422</v>
+        <v>376</v>
       </c>
       <c r="L89" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M89" s="5" t="s">
-        <v>165</v>
+        <v>398</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C90" s="4">
         <v>40.691065000000002</v>
@@ -5664,24 +5662,24 @@
         <v>0</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K90" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M90" s="5" t="s">
-        <v>165</v>
+        <v>398</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C91" s="4">
         <v>40.685864000000002</v>
@@ -5706,24 +5704,24 @@
         <v>0</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M91" s="5" t="s">
-        <v>165</v>
+        <v>398</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C92" s="4">
         <v>40.466757000000001</v>
@@ -5742,31 +5740,31 @@
         <v>17</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>374</v>
+        <v>329</v>
       </c>
       <c r="I92" s="4">
         <f>4</f>
         <v>4</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>422</v>
+        <v>376</v>
       </c>
       <c r="L92" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M92" s="5" t="s">
-        <v>165</v>
+        <v>398</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C93" s="4">
         <v>40.606189000000001</v>
@@ -5791,24 +5789,24 @@
         <v>0</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K93" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M93" s="5" t="s">
-        <v>165</v>
+        <v>398</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C94" s="4">
         <v>43.306010999999998</v>
@@ -5833,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>9</v>
@@ -5842,15 +5840,15 @@
         <v>15</v>
       </c>
       <c r="M94" s="11" t="s">
-        <v>170</v>
+        <v>399</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95" s="12" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C95" s="4">
         <v>43.278744000000003</v>
@@ -5869,30 +5867,30 @@
         <v>100</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="I95" s="4">
         <v>4</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L95" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M95" s="11" t="s">
-        <v>170</v>
+        <v>399</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96" s="12" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C96" s="4">
         <v>43.278744000000003</v>
@@ -5911,13 +5909,13 @@
         <v>100</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="I96" s="4">
         <v>4</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>9</v>
@@ -5926,15 +5924,15 @@
         <v>15</v>
       </c>
       <c r="M96" s="11" t="s">
-        <v>170</v>
+        <v>399</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C97" s="4">
         <v>54.605437999999999</v>
@@ -5959,24 +5957,24 @@
         <v>0</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>375</v>
+        <v>330</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>423</v>
+        <v>377</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="M97" s="5" t="s">
-        <v>177</v>
+        <v>400</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C98" s="4">
         <v>54.613191999999998</v>
@@ -6001,24 +5999,24 @@
         <v>0</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>375</v>
+        <v>330</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>423</v>
+        <v>377</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="M98" s="5" t="s">
-        <v>177</v>
+        <v>400</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C99" s="4">
         <v>54.605567999999998</v>
@@ -6043,24 +6041,24 @@
         <v>0</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>375</v>
+        <v>330</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>423</v>
+        <v>377</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="M99" s="5" t="s">
-        <v>177</v>
+        <v>400</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" s="3" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C100" s="4">
         <v>54.613162000000003</v>
@@ -6085,24 +6083,24 @@
         <v>0</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>376</v>
+        <v>331</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>423</v>
+        <v>377</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M100" s="5" t="s">
-        <v>177</v>
+        <v>400</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C101" s="4">
         <v>47.271256999999999</v>
@@ -6121,30 +6119,30 @@
         <v>63</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>377</v>
+        <v>332</v>
       </c>
       <c r="I101" s="4">
         <v>42</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="M101" s="6" t="s">
-        <v>183</v>
+        <v>401</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A102" s="3" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C102" s="4">
         <v>47.271256999999999</v>
@@ -6163,30 +6161,30 @@
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>378</v>
+        <v>333</v>
       </c>
       <c r="I102" s="4">
         <v>10</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>183</v>
+        <v>401</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C103" s="4">
         <v>33.916406000000002</v>
@@ -6205,13 +6203,13 @@
         <v>37</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>379</v>
+        <v>334</v>
       </c>
       <c r="I103" s="4">
         <v>29</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K103" s="3" t="s">
         <v>9</v>
@@ -6220,15 +6218,15 @@
         <v>15</v>
       </c>
       <c r="M103" s="11" t="s">
-        <v>187</v>
+        <v>402</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104" s="3" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C104" s="4">
         <v>34.226624999999999</v>
@@ -6247,14 +6245,14 @@
         <v>90</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>380</v>
+        <v>335</v>
       </c>
       <c r="I104" s="4">
         <f>17+22</f>
         <v>39</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>356</v>
+        <v>312</v>
       </c>
       <c r="K104" s="3" t="s">
         <v>9</v>
@@ -6263,15 +6261,15 @@
         <v>15</v>
       </c>
       <c r="M104" s="11" t="s">
-        <v>187</v>
+        <v>402</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C105" s="4">
         <v>44.904693999999999</v>
@@ -6296,24 +6294,24 @@
         <v>0</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K105" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M105" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C106" s="4">
         <v>44.157705999999997</v>
@@ -6332,30 +6330,30 @@
         <v>19</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="I106" s="4">
         <v>58</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K106" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C107" s="4">
         <v>41.817272000000003</v>
@@ -6380,24 +6378,24 @@
         <v>0</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K107" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M107" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A108" s="3" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C108" s="4">
         <v>40.806913999999999</v>
@@ -6422,24 +6420,24 @@
         <v>0</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K108" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M108" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C109" s="4">
         <v>40.796692999999998</v>
@@ -6458,30 +6456,30 @@
         <v>71</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>381</v>
+        <v>336</v>
       </c>
       <c r="I109" s="4">
         <v>38</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K109" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M109" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C110" s="4">
         <v>40.700215999999998</v>
@@ -6500,30 +6498,30 @@
         <v>170</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>382</v>
+        <v>337</v>
       </c>
       <c r="I110" s="4">
         <v>5</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K110" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M110" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C111" s="4">
         <v>40.513271000000003</v>
@@ -6548,24 +6546,24 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K111" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M111" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C112" s="4">
         <v>37.002716999999997</v>
@@ -6584,30 +6582,30 @@
         <v>60</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>383</v>
+        <v>338</v>
       </c>
       <c r="I112" s="4">
         <v>71</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K112" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M112" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C113" s="4">
         <v>36.853709000000002</v>
@@ -6626,30 +6624,30 @@
         <v>10</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>384</v>
+        <v>339</v>
       </c>
       <c r="I113" s="4">
         <v>59</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K113" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M113" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C114" s="4">
         <v>33.915756000000002</v>
@@ -6668,30 +6666,30 @@
         <v>31</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>385</v>
+        <v>340</v>
       </c>
       <c r="I114" s="4">
         <v>73</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K114" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M114" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C115" s="4">
         <v>32.775281999999997</v>
@@ -6710,30 +6708,30 @@
         <v>36</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="I115" s="4">
         <v>20</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K115" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L115" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M115" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A116" s="3" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C116" s="4">
         <v>25.770721999999999</v>
@@ -6752,30 +6750,30 @@
         <v>53</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>386</v>
+        <v>341</v>
       </c>
       <c r="I116" s="4">
         <v>2</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K116" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L116" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M116" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A117" s="3" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C117" s="4">
         <v>30.959171000000001</v>
@@ -6800,24 +6798,24 @@
         <v>0</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K117" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M117" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A118" s="3" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C118" s="4">
         <v>30.762004000000001</v>
@@ -6842,24 +6840,24 @@
         <v>0</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K118" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M118" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C119" s="4">
         <v>30.459246</v>
@@ -6884,24 +6882,24 @@
         <v>0</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K119" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L119" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M119" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A120" s="3" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C120" s="4">
         <v>30.283428000000001</v>
@@ -6926,24 +6924,24 @@
         <v>0</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K120" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L120" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M120" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A121" s="3" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C121" s="4">
         <v>30.109304999999999</v>
@@ -6968,24 +6966,24 @@
         <v>0</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K121" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M121" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A122" s="3" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C122" s="4">
         <v>30.208877999999999</v>
@@ -7010,24 +7008,24 @@
         <v>0</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K122" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L122" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M122" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C123" s="4">
         <v>29.35737</v>
@@ -7052,24 +7050,24 @@
         <v>0</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K123" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L123" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M123" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A124" s="3" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C124" s="4">
         <v>29.920157</v>
@@ -7094,24 +7092,24 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K124" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L124" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M124" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A125" s="3" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C125" s="4">
         <v>29.952963</v>
@@ -7136,24 +7134,24 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K125" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L125" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M125" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A126" s="3" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C126" s="4">
         <v>29.250332</v>
@@ -7178,24 +7176,24 @@
         <v>0</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K126" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L126" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M126" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C127" s="4">
         <v>30.39189</v>
@@ -7214,30 +7212,30 @@
         <v>37</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>387</v>
+        <v>342</v>
       </c>
       <c r="I127" s="4">
         <v>37</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K127" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L127" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M127" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C128" s="4">
         <v>29.282572999999999</v>
@@ -7256,30 +7254,30 @@
         <v>5</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="I128" s="4">
         <v>34</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K128" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L128" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M128" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C129" s="4">
         <v>38.563921000000001</v>
@@ -7298,30 +7296,30 @@
         <v>79</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>389</v>
+        <v>344</v>
       </c>
       <c r="I129" s="4">
         <v>19</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K129" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L129" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M129" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C130" s="4">
         <v>37.856363000000002</v>
@@ -7340,30 +7338,30 @@
         <v>23</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="I130" s="4">
         <v>54</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K130" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L130" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M130" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C131" s="4">
         <v>37.810412999999997</v>
@@ -7388,24 +7386,24 @@
         <v>0</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K131" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M131" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
-        <v>220</v>
+        <v>194</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C132" s="4">
         <v>32.669840999999998</v>
@@ -7430,24 +7428,24 @@
         <v>0</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K132" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M132" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C133" s="4">
         <v>34.007829999999998</v>
@@ -7472,24 +7470,24 @@
         <v>0</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K133" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L133" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M133" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C134" s="4">
         <v>48.135519000000002</v>
@@ -7508,30 +7506,30 @@
         <v>11</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>390</v>
+        <v>345</v>
       </c>
       <c r="I134" s="4">
         <v>87</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K134" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M134" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C135" s="4">
         <v>45.622391</v>
@@ -7556,24 +7554,24 @@
         <v>25</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K135" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L135" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M135" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C136" s="4">
         <v>45.509630999999999</v>
@@ -7598,24 +7596,24 @@
         <v>0</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K136" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L136" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M136" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C137" s="4">
         <v>45.652999000000001</v>
@@ -7640,24 +7638,24 @@
         <v>0</v>
       </c>
       <c r="J137" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K137" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L137" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M137" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C138" s="4">
         <v>57.048735000000001</v>
@@ -7676,30 +7674,30 @@
         <v>6</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="I138" s="4">
         <v>30</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K138" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L138" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M138" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C139" s="4">
         <v>57.787987999999999</v>
@@ -7718,31 +7716,31 @@
         <v>43</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>391</v>
+        <v>346</v>
       </c>
       <c r="I139" s="4">
         <f>16+8+15+12</f>
         <v>51</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K139" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L139" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M139" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A140" s="3" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C140" s="4">
         <v>53.891196000000001</v>
@@ -7761,30 +7759,30 @@
         <v>40</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="I140" s="4">
         <v>6</v>
       </c>
       <c r="J140" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K140" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L140" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M140" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C141" s="4">
         <v>51.860652000000002</v>
@@ -7809,24 +7807,24 @@
         <v>0</v>
       </c>
       <c r="J141" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K141" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L141" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M141" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A142" s="3" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C142" s="4">
         <v>54.561858999999998</v>
@@ -7851,24 +7849,24 @@
         <v>0</v>
       </c>
       <c r="J142" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K142" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L142" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M142" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C143" s="4">
         <v>45.565617000000003</v>
@@ -7893,24 +7891,24 @@
         <v>0</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K143" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L143" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="M143" s="6" t="s">
-        <v>191</v>
+        <v>403</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A144" s="3" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C144" s="4">
         <v>42.368887000000001</v>
@@ -7935,24 +7933,24 @@
         <v>0</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K144" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L144" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="M144" s="5" t="s">
-        <v>234</v>
+        <v>165</v>
+      </c>
+      <c r="M144" s="29" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C145" s="4">
         <v>42.371845</v>
@@ -7977,24 +7975,24 @@
         <v>0</v>
       </c>
       <c r="J145" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K145" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L145" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="M145" s="5" t="s">
-        <v>234</v>
+        <v>165</v>
+      </c>
+      <c r="M145" s="29" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A146" s="3" t="s">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C146" s="4">
         <v>42.371845</v>
@@ -8019,24 +8017,24 @@
         <v>0</v>
       </c>
       <c r="J146" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K146" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L146" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="M146" s="5" t="s">
-        <v>234</v>
+        <v>165</v>
+      </c>
+      <c r="M146" s="29" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A147" s="3" t="s">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C147" s="4">
         <v>42.371845</v>
@@ -8061,24 +8059,24 @@
         <v>0</v>
       </c>
       <c r="J147" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K147" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L147" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="M147" s="5" t="s">
-        <v>234</v>
+        <v>165</v>
+      </c>
+      <c r="M147" s="29" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A148" s="3" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C148" s="4">
         <v>42.371845</v>
@@ -8103,24 +8101,24 @@
         <v>0</v>
       </c>
       <c r="J148" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K148" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L148" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="M148" s="5" t="s">
-        <v>234</v>
+        <v>165</v>
+      </c>
+      <c r="M148" s="29" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C149" s="4">
         <v>42.609319999999997</v>
@@ -8145,24 +8143,24 @@
         <v>0</v>
       </c>
       <c r="J149" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K149" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L149" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="M149" s="5" t="s">
-        <v>240</v>
+        <v>79</v>
+      </c>
+      <c r="M149" s="29" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A150" s="3" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C150" s="4">
         <v>40.673825000000001</v>
@@ -8187,24 +8185,24 @@
         <v>0</v>
       </c>
       <c r="J150" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K150" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L150" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M150" s="5" t="s">
-        <v>242</v>
+        <v>406</v>
       </c>
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A151" s="3" t="s">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C151" s="4">
         <v>40.689436999999998</v>
@@ -8223,30 +8221,30 @@
         <v>2</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="I151" s="4">
         <v>32</v>
       </c>
       <c r="J151" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K151" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L151" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M151" s="5" t="s">
-        <v>242</v>
+        <v>406</v>
       </c>
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A152" s="3" t="s">
-        <v>244</v>
+        <v>215</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C152" s="4">
         <v>40.854368000000001</v>
@@ -8265,30 +8263,30 @@
         <v>2</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>393</v>
+        <v>348</v>
       </c>
       <c r="I152" s="4">
         <v>18</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K152" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L152" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M152" s="5" t="s">
-        <v>242</v>
+        <v>406</v>
       </c>
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A153" s="3" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C153" s="4">
         <v>40.786419000000002</v>
@@ -8313,24 +8311,24 @@
         <v>0</v>
       </c>
       <c r="J153" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K153" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L153" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M153" s="5" t="s">
-        <v>242</v>
+        <v>406</v>
       </c>
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A154" s="3" t="s">
-        <v>246</v>
+        <v>217</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C154" s="4">
         <v>40.655414999999998</v>
@@ -8355,24 +8353,24 @@
         <v>0</v>
       </c>
       <c r="J154" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K154" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L154" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M154" s="5" t="s">
-        <v>242</v>
+        <v>406</v>
       </c>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A155" s="3" t="s">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C155" s="4">
         <v>40.641103000000001</v>
@@ -8397,24 +8395,24 @@
         <v>0</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K155" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L155" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M155" s="5" t="s">
-        <v>242</v>
+        <v>406</v>
       </c>
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A156" s="3" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C156" s="4">
         <v>40.606189000000001</v>
@@ -8439,24 +8437,24 @@
         <v>0</v>
       </c>
       <c r="J156" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K156" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L156" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M156" s="5" t="s">
-        <v>242</v>
+        <v>406</v>
       </c>
     </row>
     <row r="157" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A157" s="13" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C157" s="4">
         <v>44.487842999999998</v>
@@ -8475,22 +8473,22 @@
         <v>50</v>
       </c>
       <c r="H157" s="8" t="s">
-        <v>394</v>
+        <v>349</v>
       </c>
       <c r="I157" s="9">
         <v>12</v>
       </c>
       <c r="J157" s="8" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K157" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L157" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M157" s="5" t="s">
-        <v>249</v>
+        <v>407</v>
       </c>
       <c r="N157" s="10"/>
       <c r="O157" s="10"/>
@@ -8503,10 +8501,10 @@
     </row>
     <row r="158" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A158" s="13" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C158" s="4">
         <v>44.492660999999998</v>
@@ -8525,22 +8523,22 @@
         <v>21</v>
       </c>
       <c r="H158" s="8" t="s">
-        <v>395</v>
+        <v>350</v>
       </c>
       <c r="I158" s="9">
         <v>3</v>
       </c>
       <c r="J158" s="8" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K158" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L158" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M158" s="5" t="s">
-        <v>249</v>
+        <v>407</v>
       </c>
       <c r="N158" s="10"/>
       <c r="O158" s="10"/>
@@ -8553,10 +8551,10 @@
     </row>
     <row r="159" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A159" s="13" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C159" s="4">
         <v>44.492125999999999</v>
@@ -8581,16 +8579,16 @@
         <v>0</v>
       </c>
       <c r="J159" s="8" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K159" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L159" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M159" s="5" t="s">
-        <v>249</v>
+        <v>407</v>
       </c>
       <c r="N159" s="10"/>
       <c r="O159" s="10"/>
@@ -8603,10 +8601,10 @@
     </row>
     <row r="160" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A160" s="3" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C160" s="4">
         <v>44.904693999999999</v>
@@ -8625,22 +8623,22 @@
         <v>7</v>
       </c>
       <c r="H160" s="8" t="s">
-        <v>396</v>
+        <v>351</v>
       </c>
       <c r="I160" s="9">
         <v>24</v>
       </c>
       <c r="J160" s="8" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K160" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L160" s="3" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="M160" s="6" t="s">
-        <v>253</v>
+        <v>408</v>
       </c>
       <c r="N160" s="10"/>
       <c r="O160" s="10"/>
@@ -8653,10 +8651,10 @@
     </row>
     <row r="161" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A161" s="13" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C161" s="4">
         <v>43.658025000000002</v>
@@ -8675,22 +8673,22 @@
         <v>1.42</v>
       </c>
       <c r="H161" s="8" t="s">
-        <v>254</v>
+        <v>223</v>
       </c>
       <c r="I161" s="9">
         <v>1.58</v>
       </c>
       <c r="J161" s="8" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K161" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L161" s="3" t="s">
-        <v>255</v>
+        <v>224</v>
       </c>
       <c r="M161" s="6" t="s">
-        <v>253</v>
+        <v>408</v>
       </c>
       <c r="N161" s="10"/>
       <c r="O161" s="10"/>
@@ -8703,10 +8701,10 @@
     </row>
     <row r="162" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A162" s="3" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C162" s="4">
         <v>44.157705999999997</v>
@@ -8725,22 +8723,22 @@
         <v>8.9000000000000057</v>
       </c>
       <c r="H162" s="8" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="I162" s="9">
         <v>68.099999999999994</v>
       </c>
       <c r="J162" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K162" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L162" s="3" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="M162" s="6" t="s">
-        <v>253</v>
+        <v>408</v>
       </c>
       <c r="N162" s="10"/>
       <c r="O162" s="10"/>
@@ -8753,10 +8751,10 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A163" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C163" s="4">
         <v>46.197349000000003</v>
@@ -8781,24 +8779,24 @@
         <v>0</v>
       </c>
       <c r="J163" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K163" s="3" t="s">
-        <v>422</v>
+        <v>376</v>
       </c>
       <c r="L163" s="3" t="s">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="M163" s="5" t="s">
-        <v>262</v>
+        <v>409</v>
       </c>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A164" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C164" s="4">
         <v>46.197349000000003</v>
@@ -8817,30 +8815,30 @@
         <v>20</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>397</v>
+        <v>352</v>
       </c>
       <c r="I164" s="4">
         <v>3</v>
       </c>
       <c r="J164" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K164" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L164" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M164" s="5" t="s">
-        <v>262</v>
+        <v>409</v>
       </c>
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A165" s="3" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C165" s="4">
         <v>46.207951999999999</v>
@@ -8859,30 +8857,30 @@
         <v>33</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>367</v>
+        <v>322</v>
       </c>
       <c r="I165" s="4">
         <v>0</v>
       </c>
       <c r="J165" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K165" s="3" t="s">
-        <v>264</v>
+        <v>232</v>
       </c>
       <c r="L165" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M165" s="5" t="s">
-        <v>262</v>
+        <v>409</v>
       </c>
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A166" s="3" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C166" s="4">
         <v>46.170723000000002</v>
@@ -8907,7 +8905,7 @@
         <v>0</v>
       </c>
       <c r="J166" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K166" s="3" t="s">
         <v>9</v>
@@ -8916,15 +8914,15 @@
         <v>15</v>
       </c>
       <c r="M166" s="5" t="s">
-        <v>262</v>
+        <v>409</v>
       </c>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A167" s="3" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C167" s="4">
         <v>46.192236000000001</v>
@@ -8949,7 +8947,7 @@
         <v>0</v>
       </c>
       <c r="J167" s="3" t="s">
-        <v>355</v>
+        <v>311</v>
       </c>
       <c r="K167" s="3" t="s">
         <v>9</v>
@@ -8958,15 +8956,15 @@
         <v>15</v>
       </c>
       <c r="M167" s="5" t="s">
-        <v>262</v>
+        <v>409</v>
       </c>
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A168" s="3" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C168" s="4">
         <v>51.047192000000003</v>
@@ -8985,31 +8983,31 @@
         <v>5</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>398</v>
+        <v>353</v>
       </c>
       <c r="I168" s="4">
         <f>98+33</f>
         <v>131</v>
       </c>
       <c r="J168" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K168" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L168" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M168" s="5" t="s">
-        <v>268</v>
+        <v>410</v>
       </c>
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A169" s="3" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C169" s="4">
         <v>51.047192000000003</v>
@@ -9028,30 +9026,30 @@
         <v>24</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>399</v>
+        <v>354</v>
       </c>
       <c r="I169" s="4">
         <v>56</v>
       </c>
       <c r="J169" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K169" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L169" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="M169" s="5" t="s">
-        <v>268</v>
+        <v>410</v>
       </c>
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A170" s="3" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C170" s="4">
         <v>50.961742999999998</v>
@@ -9076,24 +9074,24 @@
         <v>0</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K170" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L170" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M170" s="5" t="s">
-        <v>268</v>
+        <v>410</v>
       </c>
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A171" s="3" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C171" s="4">
         <v>50.961742999999998</v>
@@ -9112,31 +9110,31 @@
         <v>8</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>400</v>
+        <v>355</v>
       </c>
       <c r="I171" s="4">
         <f>31+20+6</f>
         <v>57</v>
       </c>
       <c r="J171" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K171" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L171" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="M171" s="5" t="s">
-        <v>268</v>
+        <v>410</v>
       </c>
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A172" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C172" s="4">
         <v>50.728225000000002</v>
@@ -9155,30 +9153,30 @@
         <v>2</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>401</v>
+        <v>356</v>
       </c>
       <c r="I172" s="4">
         <v>19</v>
       </c>
       <c r="J172" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K172" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L172" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M172" s="5" t="s">
-        <v>268</v>
+        <v>410</v>
       </c>
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A173" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C173" s="4">
         <v>50.728225000000002</v>
@@ -9197,31 +9195,31 @@
         <v>11</v>
       </c>
       <c r="H173" s="3" t="s">
-        <v>402</v>
+        <v>357</v>
       </c>
       <c r="I173" s="4">
         <f>1+30+1+18+4+4</f>
         <v>58</v>
       </c>
       <c r="J173" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K173" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L173" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="M173" s="5" t="s">
-        <v>268</v>
+        <v>410</v>
       </c>
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A174" s="3" t="s">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C174" s="4">
         <v>38.342443000000003</v>
@@ -9246,24 +9244,24 @@
         <v>0</v>
       </c>
       <c r="J174" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K174" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L174" s="3" t="s">
-        <v>272</v>
+        <v>239</v>
       </c>
       <c r="M174" s="5" t="s">
-        <v>273</v>
+        <v>411</v>
       </c>
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A175" s="3" t="s">
-        <v>274</v>
+        <v>240</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C175" s="4">
         <v>38.337060000000001</v>
@@ -9282,31 +9280,31 @@
         <v>47.917864476386036</v>
       </c>
       <c r="H175" s="3" t="s">
-        <v>403</v>
+        <v>358</v>
       </c>
       <c r="I175" s="4">
         <f>3+(30/365.25)</f>
         <v>3.0821355236139629</v>
       </c>
       <c r="J175" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K175" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L175" s="3" t="s">
-        <v>275</v>
+        <v>241</v>
       </c>
       <c r="M175" s="5" t="s">
-        <v>273</v>
+        <v>411</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A176" s="3" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C176" s="4">
         <v>38.338338999999998</v>
@@ -9325,14 +9323,14 @@
         <v>51.915126625598901</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>404</v>
+        <v>359</v>
       </c>
       <c r="I176" s="4">
         <f>3+((31+30+31+30)/365.25)+4-((30+31+30)/365.25)+4</f>
         <v>11.084873374401095</v>
       </c>
       <c r="J176" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K176" s="3" t="s">
         <v>9</v>
@@ -9341,15 +9339,15 @@
         <v>15</v>
       </c>
       <c r="M176" s="5" t="s">
-        <v>273</v>
+        <v>411</v>
       </c>
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A177" s="13" t="s">
-        <v>277</v>
+        <v>243</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C177" s="4">
         <v>38.338338999999998</v>
@@ -9374,24 +9372,24 @@
         <v>0</v>
       </c>
       <c r="J177" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K177" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L177" s="3" t="s">
-        <v>278</v>
+        <v>244</v>
       </c>
       <c r="M177" s="5" t="s">
-        <v>273</v>
+        <v>411</v>
       </c>
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A178" s="3" t="s">
-        <v>279</v>
+        <v>245</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C178" s="4">
         <v>38.339146</v>
@@ -9416,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="J178" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K178" s="3" t="s">
         <v>9</v>
@@ -9425,15 +9423,15 @@
         <v>15</v>
       </c>
       <c r="M178" s="5" t="s">
-        <v>273</v>
+        <v>411</v>
       </c>
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A179" s="3" t="s">
-        <v>280</v>
+        <v>246</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C179" s="4">
         <v>43.466155000000001</v>
@@ -9452,30 +9450,30 @@
         <v>44</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>405</v>
+        <v>360</v>
       </c>
       <c r="I179" s="4">
         <v>5</v>
       </c>
       <c r="J179" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K179" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L179" s="3" t="s">
-        <v>275</v>
+        <v>241</v>
       </c>
       <c r="M179" s="5" t="s">
-        <v>273</v>
+        <v>411</v>
       </c>
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A180" s="3" t="s">
-        <v>281</v>
+        <v>247</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C180" s="4">
         <v>43.461438000000001</v>
@@ -9500,24 +9498,24 @@
         <v>0</v>
       </c>
       <c r="J180" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K180" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L180" s="3" t="s">
-        <v>275</v>
+        <v>241</v>
       </c>
       <c r="M180" s="5" t="s">
-        <v>273</v>
+        <v>411</v>
       </c>
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A181" s="3" t="s">
-        <v>282</v>
+        <v>248</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C181" s="4">
         <v>43.461438000000001</v>
@@ -9542,24 +9540,24 @@
         <v>0</v>
       </c>
       <c r="J181" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K181" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L181" s="3" t="s">
-        <v>275</v>
+        <v>241</v>
       </c>
       <c r="M181" s="5" t="s">
-        <v>273</v>
+        <v>411</v>
       </c>
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A182" s="3" t="s">
-        <v>283</v>
+        <v>249</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C182" s="4">
         <v>50.712321000000003</v>
@@ -9578,30 +9576,30 @@
         <v>4</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>406</v>
+        <v>361</v>
       </c>
       <c r="I182" s="4">
         <v>49</v>
       </c>
       <c r="J182" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K182" s="3" t="s">
-        <v>422</v>
+        <v>376</v>
       </c>
       <c r="L182" s="3" t="s">
-        <v>284</v>
+        <v>250</v>
       </c>
       <c r="M182" s="5" t="s">
-        <v>285</v>
+        <v>412</v>
       </c>
     </row>
     <row r="183" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A183" s="3" t="s">
-        <v>286</v>
+        <v>251</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C183" s="4">
         <v>30.398299999999999</v>
@@ -9626,7 +9624,7 @@
         <v>0</v>
       </c>
       <c r="J183" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K183" s="3" t="s">
         <v>9</v>
@@ -9635,7 +9633,7 @@
         <v>15</v>
       </c>
       <c r="M183" s="6" t="s">
-        <v>287</v>
+        <v>413</v>
       </c>
       <c r="N183" s="10"/>
       <c r="O183" s="10"/>
@@ -9648,10 +9646,10 @@
     </row>
     <row r="184" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A184" s="3" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C184" s="4">
         <v>30.322700000000001</v>
@@ -9676,16 +9674,16 @@
         <v>0</v>
       </c>
       <c r="J184" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K184" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L184" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M184" s="6" t="s">
-        <v>287</v>
+        <v>413</v>
       </c>
       <c r="N184" s="10"/>
       <c r="O184" s="10"/>
@@ -9698,10 +9696,10 @@
     </row>
     <row r="185" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A185" s="3" t="s">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C185" s="4">
         <v>30.370425000000001</v>
@@ -9720,22 +9718,22 @@
         <v>24</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>407</v>
+        <v>362</v>
       </c>
       <c r="I185" s="4">
         <v>17</v>
       </c>
       <c r="J185" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K185" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L185" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M185" s="6" t="s">
-        <v>287</v>
+        <v>413</v>
       </c>
       <c r="N185" s="10"/>
       <c r="O185" s="10"/>
@@ -9748,10 +9746,10 @@
     </row>
     <row r="186" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A186" s="3" t="s">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>11</v>
@@ -9770,22 +9768,22 @@
         <v>2</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>408</v>
+        <v>363</v>
       </c>
       <c r="I186" s="4">
         <v>12</v>
       </c>
       <c r="J186" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K186" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L186" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M186" s="6" t="s">
-        <v>287</v>
+        <v>413</v>
       </c>
       <c r="N186" s="10"/>
       <c r="O186" s="10"/>
@@ -9798,7 +9796,7 @@
     </row>
     <row r="187" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A187" s="3" t="s">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>13</v>
@@ -9826,7 +9824,7 @@
         <v>0.75</v>
       </c>
       <c r="J187" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K187" s="3" t="s">
         <v>9</v>
@@ -9835,7 +9833,7 @@
         <v>15</v>
       </c>
       <c r="M187" s="6" t="s">
-        <v>292</v>
+        <v>414</v>
       </c>
       <c r="N187" s="10"/>
       <c r="O187" s="10"/>
@@ -9848,7 +9846,7 @@
     </row>
     <row r="188" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A188" s="3" t="s">
-        <v>293</v>
+        <v>256</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>13</v>
@@ -9876,7 +9874,7 @@
         <v>0</v>
       </c>
       <c r="J188" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K188" s="3" t="s">
         <v>9</v>
@@ -9885,7 +9883,7 @@
         <v>15</v>
       </c>
       <c r="M188" s="6" t="s">
-        <v>292</v>
+        <v>414</v>
       </c>
       <c r="N188" s="10"/>
       <c r="O188" s="10"/>
@@ -9898,10 +9896,10 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A189" s="3" t="s">
-        <v>294</v>
+        <v>257</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C189" s="4">
         <v>51.842799999999997</v>
@@ -9926,24 +9924,24 @@
         <v>1</v>
       </c>
       <c r="J189" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K189" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L189" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M189" s="5" t="s">
-        <v>295</v>
+        <v>415</v>
       </c>
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A190" s="3" t="s">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C190" s="4">
         <v>51.391399999999997</v>
@@ -9968,24 +9966,24 @@
         <v>1</v>
       </c>
       <c r="J190" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K190" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L190" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M190" s="5" t="s">
-        <v>295</v>
+        <v>415</v>
       </c>
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A191" s="3" t="s">
-        <v>297</v>
+        <v>259</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C191" s="4">
         <v>51.472299999999997</v>
@@ -10010,24 +10008,24 @@
         <v>0</v>
       </c>
       <c r="J191" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K191" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L191" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M191" s="5" t="s">
-        <v>295</v>
+        <v>415</v>
       </c>
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A192" s="3" t="s">
-        <v>258</v>
+        <v>227</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C192" s="4">
         <v>51.5139</v>
@@ -10052,24 +10050,24 @@
         <v>0</v>
       </c>
       <c r="J192" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K192" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L192" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M192" s="5" t="s">
-        <v>295</v>
+        <v>415</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A193" s="3" t="s">
-        <v>298</v>
+        <v>260</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C193" s="4">
         <v>51.504100000000001</v>
@@ -10094,24 +10092,24 @@
         <v>0</v>
       </c>
       <c r="J193" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K193" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L193" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M193" s="5" t="s">
-        <v>295</v>
+        <v>415</v>
       </c>
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A194" s="3" t="s">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C194" s="4">
         <v>51.456200000000003</v>
@@ -10136,24 +10134,24 @@
         <v>0</v>
       </c>
       <c r="J194" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K194" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L194" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M194" s="5" t="s">
-        <v>295</v>
+        <v>415</v>
       </c>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A195" s="3" t="s">
-        <v>299</v>
+        <v>261</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C195" s="4">
         <v>51.506900000000002</v>
@@ -10172,30 +10170,30 @@
         <v>36</v>
       </c>
       <c r="H195" s="3" t="s">
-        <v>409</v>
+        <v>364</v>
       </c>
       <c r="I195" s="4">
         <v>40</v>
       </c>
       <c r="J195" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K195" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L195" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M195" s="5" t="s">
-        <v>295</v>
+        <v>415</v>
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A196" s="3" t="s">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C196" s="4">
         <v>51.498199999999997</v>
@@ -10220,24 +10218,24 @@
         <v>0</v>
       </c>
       <c r="J196" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K196" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L196" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M196" s="5" t="s">
-        <v>295</v>
+        <v>415</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A197" s="3" t="s">
-        <v>301</v>
+        <v>263</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C197" s="4">
         <v>51.501300000000001</v>
@@ -10262,24 +10260,24 @@
         <v>0</v>
       </c>
       <c r="J197" s="3" t="s">
-        <v>355</v>
+        <v>311</v>
       </c>
       <c r="K197" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L197" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M197" s="5" t="s">
-        <v>295</v>
+        <v>415</v>
       </c>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A198" s="3" t="s">
-        <v>260</v>
+        <v>229</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C198" s="4">
         <v>51.506999999999998</v>
@@ -10304,24 +10302,24 @@
         <v>0</v>
       </c>
       <c r="J198" s="3" t="s">
-        <v>355</v>
+        <v>311</v>
       </c>
       <c r="K198" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L198" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M198" s="5" t="s">
-        <v>295</v>
+        <v>415</v>
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A199" s="3" t="s">
-        <v>302</v>
+        <v>264</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C199" s="4">
         <v>51.507199999999997</v>
@@ -10346,24 +10344,24 @@
         <v>0</v>
       </c>
       <c r="J199" s="3" t="s">
-        <v>355</v>
+        <v>311</v>
       </c>
       <c r="K199" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L199" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M199" s="5" t="s">
-        <v>295</v>
+        <v>415</v>
       </c>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A200" s="3" t="s">
-        <v>303</v>
+        <v>265</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C200" s="4">
         <v>51.446800000000003</v>
@@ -10389,24 +10387,24 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="J200" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K200" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L200" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M200" s="5" t="s">
-        <v>295</v>
+        <v>415</v>
       </c>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A201" s="3" t="s">
-        <v>304</v>
+        <v>266</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C201" s="4">
         <v>51.5107</v>
@@ -10431,24 +10429,24 @@
         <v>0</v>
       </c>
       <c r="J201" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K201" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L201" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M201" s="5" t="s">
-        <v>295</v>
+        <v>415</v>
       </c>
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A202" s="3" t="s">
-        <v>305</v>
+        <v>267</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C202" s="4">
         <v>51.486699999999999</v>
@@ -10473,24 +10471,24 @@
         <v>0</v>
       </c>
       <c r="J202" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K202" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L202" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M202" s="5" t="s">
-        <v>295</v>
+        <v>415</v>
       </c>
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A203" s="3" t="s">
-        <v>306</v>
+        <v>268</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C203" s="4">
         <v>51.462299999999999</v>
@@ -10515,24 +10513,24 @@
         <v>0</v>
       </c>
       <c r="J203" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K203" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L203" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M203" s="5" t="s">
-        <v>295</v>
+        <v>415</v>
       </c>
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A204" s="3" t="s">
-        <v>307</v>
+        <v>269</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C204" s="4">
         <v>43.395269999999996</v>
@@ -10551,31 +10549,31 @@
         <v>54.5</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>410</v>
+        <v>365</v>
       </c>
       <c r="I204" s="4">
         <f>6+0.5+2</f>
         <v>8.5</v>
       </c>
       <c r="J204" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K204" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L204" s="3" t="s">
-        <v>308</v>
+        <v>270</v>
       </c>
       <c r="M204" s="6" t="s">
-        <v>309</v>
+        <v>416</v>
       </c>
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A205" s="3" t="s">
-        <v>307</v>
+        <v>269</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C205" s="4">
         <v>43.395269999999996</v>
@@ -10600,7 +10598,7 @@
         <v>0</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K205" s="3" t="s">
         <v>9</v>
@@ -10609,15 +10607,15 @@
         <v>15</v>
       </c>
       <c r="M205" s="6" t="s">
-        <v>357</v>
+        <v>416</v>
       </c>
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A206" s="14" t="s">
-        <v>310</v>
+        <v>271</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>311</v>
+        <v>272</v>
       </c>
       <c r="C206" s="4">
         <v>5.3038499999999997</v>
@@ -10642,24 +10640,24 @@
         <v>0</v>
       </c>
       <c r="J206" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K206" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L206" s="15" t="s">
         <v>15</v>
       </c>
       <c r="M206" s="6" t="s">
-        <v>312</v>
+        <v>417</v>
       </c>
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A207" s="3" t="s">
-        <v>313</v>
+        <v>273</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C207" s="4">
         <v>-37</v>
@@ -10678,30 +10676,30 @@
         <v>35</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>411</v>
+        <v>366</v>
       </c>
       <c r="I207" s="4">
         <v>4</v>
       </c>
       <c r="J207" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K207" s="3" t="s">
-        <v>358</v>
+        <v>313</v>
       </c>
       <c r="L207" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M207" s="16" t="s">
-        <v>314</v>
+        <v>418</v>
       </c>
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A208" s="3" t="s">
-        <v>313</v>
+        <v>273</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C208" s="4">
         <v>-37</v>
@@ -10720,27 +10718,27 @@
         <v>91</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>412</v>
+        <v>367</v>
       </c>
       <c r="I208" s="4">
         <v>4</v>
       </c>
       <c r="J208" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K208" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L208" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M208" s="16" t="s">
-        <v>314</v>
+        <v>418</v>
       </c>
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A209" s="17" t="s">
-        <v>315</v>
+        <v>274</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>13</v>
@@ -10762,31 +10760,31 @@
         <v>4.3531827515400412</v>
       </c>
       <c r="H209" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I209" s="4">
         <f>7-((288+226+222+218+299+105+232)/365.25)</f>
         <v>2.6468172484599588</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K209" s="3" t="s">
-        <v>421</v>
+        <v>375</v>
       </c>
       <c r="L209" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M209" s="5" t="s">
-        <v>316</v>
+        <v>419</v>
       </c>
     </row>
     <row r="210" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A210" s="18" t="s">
-        <v>317</v>
+        <v>275</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C210" s="19">
         <v>38.588610000000003</v>
@@ -10805,31 +10803,31 @@
         <v>74</v>
       </c>
       <c r="H210" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I210" s="4">
         <f>(F210-E210)-G210</f>
         <v>31</v>
       </c>
       <c r="J210" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K210" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L210" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M210" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A211" s="18" t="s">
-        <v>319</v>
+        <v>276</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C211" s="19">
         <v>38.349580000000003</v>
@@ -10848,31 +10846,31 @@
         <v>78</v>
       </c>
       <c r="H211" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I211" s="4">
         <f t="shared" ref="I211:I234" si="3">(F211-E211)-G211</f>
         <v>2</v>
       </c>
       <c r="J211" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K211" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L211" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M211" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A212" s="18" t="s">
-        <v>320</v>
+        <v>277</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C212" s="19">
         <v>38.255279999999999</v>
@@ -10891,31 +10889,31 @@
         <v>62.1</v>
       </c>
       <c r="H212" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I212" s="4">
         <f t="shared" si="3"/>
         <v>2.8999999999999986</v>
       </c>
       <c r="J212" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K212" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L212" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M212" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A213" s="18" t="s">
-        <v>321</v>
+        <v>278</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C213" s="4">
         <v>38.239469999999997</v>
@@ -10934,31 +10932,31 @@
         <v>74.900000000000006</v>
       </c>
       <c r="H213" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I213" s="4">
         <f t="shared" si="3"/>
         <v>20.099999999999994</v>
       </c>
       <c r="J213" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K213" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L213" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M213" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A214" s="18" t="s">
-        <v>322</v>
+        <v>279</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C214" s="4">
         <v>38.225499999999997</v>
@@ -10977,31 +10975,31 @@
         <v>98</v>
       </c>
       <c r="H214" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I214" s="4">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J214" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K214" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L214" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M214" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A215" s="18" t="s">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C215" s="19">
         <v>38.15972</v>
@@ -11020,31 +11018,31 @@
         <v>78.7</v>
       </c>
       <c r="H215" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I215" s="4">
         <f t="shared" si="3"/>
         <v>30.299999999999997</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K215" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L215" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M215" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A216" s="18" t="s">
-        <v>324</v>
+        <v>281</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C216" s="4">
         <v>38.1295</v>
@@ -11063,31 +11061,31 @@
         <v>63.2</v>
       </c>
       <c r="H216" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I216" s="4">
         <f t="shared" si="3"/>
         <v>16.799999999999997</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K216" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L216" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M216" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A217" s="18" t="s">
-        <v>325</v>
+        <v>282</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C217" s="4">
         <v>38.104999999999997</v>
@@ -11106,31 +11104,31 @@
         <v>25.9</v>
       </c>
       <c r="H217" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I217" s="4">
         <f t="shared" si="3"/>
         <v>14.100000000000001</v>
       </c>
       <c r="J217" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K217" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L217" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M217" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A218" s="17" t="s">
-        <v>326</v>
+        <v>283</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C218" s="4">
         <v>38.073610000000002</v>
@@ -11149,31 +11147,31 @@
         <v>65.8</v>
       </c>
       <c r="H218" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I218" s="4">
         <f t="shared" si="3"/>
         <v>43.2</v>
       </c>
       <c r="J218" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K218" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L218" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M218" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A219" s="17" t="s">
-        <v>327</v>
+        <v>284</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C219" s="4">
         <v>38.040559999999999</v>
@@ -11192,31 +11190,31 @@
         <v>55.8</v>
       </c>
       <c r="H219" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I219" s="4">
         <f t="shared" si="3"/>
         <v>24.200000000000003</v>
       </c>
       <c r="J219" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K219" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L219" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M219" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A220" s="17" t="s">
-        <v>328</v>
+        <v>285</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C220" s="4">
         <v>38.017780000000002</v>
@@ -11235,31 +11233,31 @@
         <v>74.599999999999994</v>
       </c>
       <c r="H220" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I220" s="4">
         <f t="shared" si="3"/>
         <v>15.400000000000006</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K220" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L220" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M220" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="221" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A221" s="17" t="s">
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C221" s="4">
         <v>38.10333</v>
@@ -11278,31 +11276,31 @@
         <v>56.3</v>
       </c>
       <c r="H221" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I221" s="4">
         <f t="shared" si="3"/>
         <v>7.7000000000000028</v>
       </c>
       <c r="J221" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K221" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L221" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M221" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A222" s="17" t="s">
-        <v>330</v>
+        <v>287</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C222" s="4">
         <v>38.090000000000003</v>
@@ -11321,31 +11319,31 @@
         <v>67</v>
       </c>
       <c r="H222" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I222" s="4">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="J222" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K222" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L222" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M222" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="223" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="21" t="s">
-        <v>331</v>
+        <v>288</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C223" s="4">
         <v>38.050229999999999</v>
@@ -11364,31 +11362,31 @@
         <v>78.8</v>
       </c>
       <c r="H223" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I223" s="4">
         <f t="shared" si="3"/>
         <v>17.200000000000003</v>
       </c>
       <c r="J223" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K223" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L223" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M223" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A224" s="17" t="s">
-        <v>332</v>
+        <v>289</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C224" s="4">
         <v>38.001719999999999</v>
@@ -11407,31 +11405,31 @@
         <v>59.2</v>
       </c>
       <c r="H224" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I224" s="4">
         <f t="shared" si="3"/>
         <v>7.7999999999999972</v>
       </c>
       <c r="J224" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K224" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L224" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M224" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A225" s="17" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C225" s="4">
         <v>37.997219999999999</v>
@@ -11450,31 +11448,31 @@
         <v>70.599999999999994</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I225" s="4">
         <f t="shared" si="3"/>
         <v>14.400000000000006</v>
       </c>
       <c r="J225" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K225" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L225" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M225" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A226" s="17" t="s">
-        <v>334</v>
+        <v>291</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C226" s="4">
         <v>37.990279999999998</v>
@@ -11493,31 +11491,31 @@
         <v>55.5</v>
       </c>
       <c r="H226" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I226" s="4">
         <f t="shared" si="3"/>
         <v>23.5</v>
       </c>
       <c r="J226" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K226" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L226" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M226" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A227" s="17" t="s">
-        <v>335</v>
+        <v>292</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C227" s="4">
         <v>37.962710000000001</v>
@@ -11536,31 +11534,31 @@
         <v>61</v>
       </c>
       <c r="H227" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I227" s="4">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K227" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L227" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M227" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A228" s="17" t="s">
-        <v>336</v>
+        <v>293</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C228" s="4">
         <v>37.890830000000001</v>
@@ -11579,31 +11577,31 @@
         <v>69.400000000000006</v>
       </c>
       <c r="H228" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I228" s="4">
         <f t="shared" si="3"/>
         <v>10.599999999999994</v>
       </c>
       <c r="J228" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K228" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L228" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M228" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A229" s="17" t="s">
-        <v>337</v>
+        <v>294</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C229" s="4">
         <v>37.864629999999998</v>
@@ -11622,31 +11620,31 @@
         <v>59</v>
       </c>
       <c r="H229" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I229" s="4">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="J229" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K229" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L229" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M229" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A230" s="17" t="s">
-        <v>338</v>
+        <v>295</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C230" s="4">
         <v>37.835279999999997</v>
@@ -11665,31 +11663,31 @@
         <v>60</v>
       </c>
       <c r="H230" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I230" s="4">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="J230" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K230" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L230" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M230" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A231" s="17" t="s">
-        <v>339</v>
+        <v>296</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C231" s="4">
         <v>37.828690000000002</v>
@@ -11708,31 +11706,31 @@
         <v>61</v>
       </c>
       <c r="H231" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I231" s="4">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="J231" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K231" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L231" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M231" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A232" s="17" t="s">
-        <v>340</v>
+        <v>297</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C232" s="4">
         <v>37.820140000000002</v>
@@ -11751,31 +11749,31 @@
         <v>52.8</v>
       </c>
       <c r="H232" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I232" s="4">
         <f t="shared" si="3"/>
         <v>13.200000000000003</v>
       </c>
       <c r="J232" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K232" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L232" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M232" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A233" s="17" t="s">
-        <v>341</v>
+        <v>298</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C233" s="4">
         <v>37.804810000000003</v>
@@ -11794,31 +11792,31 @@
         <v>61.5</v>
       </c>
       <c r="H233" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I233" s="4">
         <f t="shared" si="3"/>
         <v>5.5</v>
       </c>
       <c r="J233" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K233" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L233" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M233" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A234" s="17" t="s">
-        <v>342</v>
+        <v>299</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C234" s="4">
         <v>37.786140000000003</v>
@@ -11837,31 +11835,31 @@
         <v>45.8</v>
       </c>
       <c r="H234" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I234" s="4">
         <f t="shared" si="3"/>
         <v>58.2</v>
       </c>
       <c r="J234" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K234" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L234" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M234" s="6" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A235" s="22" t="s">
-        <v>413</v>
+        <v>368</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C235" s="23">
         <v>79.919178000000002</v>
@@ -11880,13 +11878,13 @@
         <v>0.29000000000000004</v>
       </c>
       <c r="H235" s="20" t="s">
-        <v>414</v>
+        <v>369</v>
       </c>
       <c r="I235" s="4">
         <v>0.71</v>
       </c>
       <c r="J235" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K235" s="3" t="s">
         <v>9</v>
@@ -11895,15 +11893,15 @@
         <v>15</v>
       </c>
       <c r="M235" s="5" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A236" s="22" t="s">
-        <v>353</v>
+        <v>309</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C236" s="23">
         <v>79.875488000000004</v>
@@ -11922,30 +11920,30 @@
         <v>0.29000000000000004</v>
       </c>
       <c r="H236" s="20" t="s">
-        <v>416</v>
+        <v>370</v>
       </c>
       <c r="I236" s="4">
         <v>1.71</v>
       </c>
       <c r="J236" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K236" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L236" s="3" t="s">
-        <v>417</v>
+        <v>371</v>
       </c>
       <c r="M236" s="5" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A237" s="22" t="s">
-        <v>418</v>
+        <v>372</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C237" s="23">
         <v>79.718778</v>
@@ -11964,13 +11962,13 @@
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="H237" s="20" t="s">
-        <v>419</v>
+        <v>373</v>
       </c>
       <c r="I237" s="4">
         <v>0.9</v>
       </c>
       <c r="J237" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K237" s="3" t="s">
         <v>9</v>
@@ -11979,15 +11977,15 @@
         <v>15</v>
       </c>
       <c r="M237" s="5" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A238" s="3" t="s">
-        <v>343</v>
+        <v>300</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C238" s="4">
         <v>53.4</v>
@@ -12012,24 +12010,24 @@
         <v>0</v>
       </c>
       <c r="J238" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K238" s="3" t="s">
-        <v>362</v>
+        <v>317</v>
       </c>
       <c r="L238" s="3" t="s">
-        <v>344</v>
+        <v>301</v>
       </c>
       <c r="M238" s="5" t="s">
-        <v>345</v>
+        <v>422</v>
       </c>
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A239" s="3" t="s">
-        <v>346</v>
+        <v>302</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C239" s="4">
         <v>53.383333</v>
@@ -12054,24 +12052,24 @@
         <v>0</v>
       </c>
       <c r="J239" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K239" s="3" t="s">
-        <v>362</v>
+        <v>317</v>
       </c>
       <c r="L239" s="3" t="s">
-        <v>344</v>
+        <v>301</v>
       </c>
       <c r="M239" s="5" t="s">
-        <v>345</v>
+        <v>422</v>
       </c>
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A240" s="3" t="s">
-        <v>347</v>
+        <v>303</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="C240" s="4">
         <v>1.2865660000000001</v>
@@ -12090,30 +12088,30 @@
         <v>1.5</v>
       </c>
       <c r="H240" s="3" t="s">
-        <v>349</v>
+        <v>305</v>
       </c>
       <c r="I240" s="4">
         <v>6.5</v>
       </c>
       <c r="J240" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K240" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L240" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M240" s="28" t="s">
-        <v>420</v>
+        <v>374</v>
       </c>
     </row>
     <row r="241" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A241" s="3" t="s">
-        <v>350</v>
+        <v>306</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="C241" s="7">
         <v>1.2669999999999999</v>
@@ -12132,30 +12130,30 @@
         <v>1</v>
       </c>
       <c r="H241" s="3" t="s">
-        <v>367</v>
+        <v>322</v>
       </c>
       <c r="I241" s="4">
         <v>0</v>
       </c>
       <c r="J241" s="3" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="K241" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L241" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M241" s="28" t="s">
-        <v>420</v>
+        <v>374</v>
       </c>
     </row>
     <row r="242" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A242" s="3" t="s">
-        <v>351</v>
+        <v>307</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="C242" s="7">
         <v>1.4670000000000001</v>
@@ -12174,22 +12172,22 @@
         <v>8.9999999999999969E-2</v>
       </c>
       <c r="H242" s="3" t="s">
-        <v>352</v>
+        <v>308</v>
       </c>
       <c r="I242" s="4">
         <v>0.91</v>
       </c>
       <c r="J242" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K242" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L242" s="3" t="s">
         <v>15</v>
       </c>
       <c r="M242" s="28" t="s">
-        <v>420</v>
+        <v>374</v>
       </c>
     </row>
     <row r="243" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
@@ -12281,116 +12279,161 @@
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="M209" r:id="rId1" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.256" xr:uid="{3B3BC2EB-07A7-4388-8DE3-0B4BE623A44F}"/>
-    <hyperlink ref="M238" r:id="rId2" display="https://www.zooniverse.org/projects/psmsl/uk-tides" xr:uid="{76D41B0C-176D-4DCA-A7B0-148F54D438D6}"/>
-    <hyperlink ref="M189" r:id="rId3" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{ED199385-3869-42EF-8C0C-B78D855CFBD6}"/>
-    <hyperlink ref="M207" r:id="rId4" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2024JC020908" xr:uid="{1EC0D7B3-38E6-4FC7-B9BD-8BE20F164A1C}"/>
-    <hyperlink ref="M39" r:id="rId5" display="https://link.springer.com/article/10.1007/s10236-005-0044-z" xr:uid="{816A265D-F134-497B-A21D-C66AAD7C76C0}"/>
-    <hyperlink ref="M54" r:id="rId6" display="https://www.sciencedirect.com/science/article/pii/S0278434309002313" xr:uid="{07E3CD6B-5FC6-4613-81A2-BE92995204E2}"/>
-    <hyperlink ref="M59" r:id="rId7" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2010JC006404" xr:uid="{31D74E63-CDB0-4403-853F-8D303ABE669E}"/>
-    <hyperlink ref="M60" r:id="rId8" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2010JC006113" xr:uid="{B8688911-0B7D-4852-B0CF-0DFBB3375335}"/>
-    <hyperlink ref="M62" r:id="rId9" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2011JC007558" xr:uid="{1ADFE9F5-747D-4123-826A-32BB24BDB434}"/>
-    <hyperlink ref="M63" r:id="rId10" display="https://www.tandfonline.com/doi/abs/10.2989/1814232X.2012.689623?casa_token=zBny8ik3tAMAAAAA:D-WLZrlhXskUGl1Xag8khGwd83rNrPI2GZ94RlKOsCvfW4t4DDubKDq8PhmhPgZCerNLRIoGbCBZ" xr:uid="{4C768480-6874-45BB-92EA-9286217F3F37}"/>
-    <hyperlink ref="M66" r:id="rId11" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/jgrc.20377" xr:uid="{3A020A2D-C1B0-4BFF-A75B-E2BA82C558E1}"/>
-    <hyperlink ref="M69" r:id="rId12" location="s0010" xr:uid="{5D4F4102-E9A8-44C3-BB8A-D949EFF93A74}"/>
-    <hyperlink ref="M89" r:id="rId13" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/2014GL059574" xr:uid="{E0E660CB-C13D-47E2-8CC7-02F3466E9404}"/>
-    <hyperlink ref="M94" r:id="rId14" display="https://link.springer.com/article/10.1007/s00190-014-0728-6" xr:uid="{41974C0D-C899-48E3-B8F9-A1F3596FE7C8}"/>
-    <hyperlink ref="M97" r:id="rId15" display="https://www.researchgate.net/publication/273705568_Maintaining_legacy_data_Saving_Belfast_Harbour_UK_tide-gauge_data_1901-2010" xr:uid="{026E0DB0-2AC2-4E39-818F-DFF0A4364143}"/>
-    <hyperlink ref="M144" r:id="rId16" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2017JC013645" xr:uid="{36630FE6-A1DD-44CA-8A30-589355B09684}"/>
-    <hyperlink ref="M157" r:id="rId17" location="Sec2" display="https://link.springer.com/article/10.1007/s00190-019-01238-w - Sec2" xr:uid="{3B4D3AAC-47CF-4508-9018-C84A5684680D}"/>
-    <hyperlink ref="M163" r:id="rId18" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2019JC015656" xr:uid="{6F125413-61E1-4C9B-B5C2-7CB8E424AB2D}"/>
-    <hyperlink ref="M168" r:id="rId19" display="https://theses.hal.science/tel-02899411/" xr:uid="{6F67BA82-1D7E-4810-A272-90552C4A9357}"/>
-    <hyperlink ref="M174" r:id="rId20" display="https://rmets.onlinelibrary.wiley.com/doi/full/10.1002/gdj3.112" xr:uid="{D02339E2-CA26-404B-A61B-AB45E74ECDF4}"/>
-    <hyperlink ref="M182" r:id="rId21" display="https://southerncoastalgroup-scopac.org.uk/wp-content/uploads/2022/01/Digitisation-and-Analysis-of-Poole-Harbour-Tide-Gauge-Record-September-2021.pdf" xr:uid="{087F2AC3-495E-41CB-8107-0AD10D64D954}"/>
-    <hyperlink ref="M103" r:id="rId22" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/2016GL069494" xr:uid="{EB67F5C1-0C5A-4FC9-863D-B122ABBD3ADE}"/>
-    <hyperlink ref="M149" r:id="rId23" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2018JC014313" xr:uid="{8CE25D1A-A494-4B0E-B2E9-C784377A66A0}"/>
-    <hyperlink ref="M150" r:id="rId24" display="https://link.springer.com/article/10.1007/s12237-018-0379-6" xr:uid="{6E602822-A462-413C-8556-FBD612C4A3B6}"/>
-    <hyperlink ref="M70" r:id="rId25" location="s0010" display="https://www.sciencedirect.com/science/article/pii/S0278434313001283 - s0010" xr:uid="{7CD29A62-C61A-499A-9413-7485E33AA6F4}"/>
-    <hyperlink ref="M187" r:id="rId26" location="section2" display="https://os.copernicus.org/articles/17/1623/2021/ - section2" xr:uid="{1ECF59C1-51FE-416C-B411-4182A18F1416}"/>
-    <hyperlink ref="M204" r:id="rId27" display="https://hal.science/hal-04555208v1/file/Khan2023.pdf" xr:uid="{1A6970FE-A26E-4EA7-9AEE-2D24E9C09FD3}"/>
-    <hyperlink ref="M183" r:id="rId28" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2020JC016328" xr:uid="{FA6BC1BC-4762-4794-9633-B5608B70ADD3}"/>
-    <hyperlink ref="M105" r:id="rId29" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{B808C8C8-0DCC-4FCA-96E6-921E91B8BECB}"/>
-    <hyperlink ref="M45" r:id="rId30" display="https://journals.ametsoc.org/view/journals/phoc/36/6/jpo2876.1.xml" xr:uid="{348972A7-D69E-41EA-B213-F21ABAD15781}"/>
-    <hyperlink ref="M38" r:id="rId31" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2003GL019166" xr:uid="{65041048-45D4-4A88-8A43-B70DDDE6FEA4}"/>
-    <hyperlink ref="M75" r:id="rId32" display="https://link.springer.com/article/10.1007/s10236-013-0598-0" xr:uid="{9D755DE4-521D-4B8D-9C65-0427B55C8416}"/>
-    <hyperlink ref="M2" r:id="rId33" display="https://academic.oup.com/gji/article/71/3/809/656230?login=true" xr:uid="{F25384DA-537D-4664-827D-260498FC7D86}"/>
-    <hyperlink ref="M77" r:id="rId34" display="https://meridian.allenpress.com/jcr/article/29/6a/118/144016/Nineteenth-Century-North-American-and-Pacific" xr:uid="{2016EA30-A594-4407-8F5F-279AEDDADE01}"/>
-    <hyperlink ref="M5" r:id="rId35" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{F03F33AB-5737-44E5-A79E-5DE5AD20FBBF}"/>
-    <hyperlink ref="M47" r:id="rId36" location="tocto1n3" display="https://journals.openedition.org/mediterranee/170 - tocto1n3" xr:uid="{3B721DAD-78FD-4AA2-8682-8B4B59E79EBC}"/>
-    <hyperlink ref="M206" r:id="rId37" display="https://www.scirp.org/journal/paperinformation?paperid=128406" xr:uid="{7CF77CDA-0932-47C2-8F01-5A69B8E9B95B}"/>
-    <hyperlink ref="M64" r:id="rId38" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2011JF001964" xr:uid="{B49BB6E5-677B-453E-A173-704444C8F1CE}"/>
-    <hyperlink ref="M53" r:id="rId39" location="sec2" display="https://www.sciencedirect.com/science/article/pii/S0278434306003888 - sec2" xr:uid="{51823FDB-4EC1-4D30-AB2C-45AF9D37C653}"/>
-    <hyperlink ref="M61" r:id="rId40" display="https://academic.oup.com/gji/article/182/2/781/571033" xr:uid="{C303579C-BF46-444C-B4B4-DE4965DD1413}"/>
-    <hyperlink ref="M101" r:id="rId41" display="https://refmar.shom.fr/sites/default/files/2024-07/Reconstruction serie maregraphique Saint-Nazaire par Yann Ferret 2016.pdf" xr:uid="{F718EBEC-AFF1-4288-85FD-09F2ACC52B61}"/>
-    <hyperlink ref="M160" r:id="rId42" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2019JC015277" xr:uid="{427A19E3-8871-462D-B2ED-4EDE1648EF46}"/>
-    <hyperlink ref="M36" r:id="rId43" display="https://journals.ametsoc.org/view/journals/clim/16/6/1520-0442_2003_016_0982_svatcc_2.0.co_2.xml" xr:uid="{B2133F64-8E98-4B08-85FE-47C26DDB02FF}"/>
-    <hyperlink ref="M210" r:id="rId44" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{9C3A377D-F241-4EF5-A93C-F5BBC0124F88}"/>
-    <hyperlink ref="M44" r:id="rId45" display="https://link.springer.com/article/10.1007/s10236-005-0056-8" xr:uid="{9D9BD6F8-E0D2-4BDC-BE5A-DC3A2829BCE9}"/>
-    <hyperlink ref="M6" r:id="rId46" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{49FEE0DC-656C-4429-A438-502AF915F2FD}"/>
-    <hyperlink ref="M7" r:id="rId47" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{B9B0EF45-AE8F-4A09-A98B-85F4A80837E9}"/>
-    <hyperlink ref="M9" r:id="rId48" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{A912608B-B857-421D-B8C6-4FFD280267F4}"/>
-    <hyperlink ref="M11" r:id="rId49" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{4F6F510C-D173-48D2-8E9D-5269F51EE211}"/>
-    <hyperlink ref="M13" r:id="rId50" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{1DB76D0F-A851-4C95-863A-F205311759BF}"/>
-    <hyperlink ref="M15" r:id="rId51" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{93B84B86-B5DB-4B51-83A5-2033D299C71E}"/>
-    <hyperlink ref="M17" r:id="rId52" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{A976754E-7320-4F9F-994C-F6C7CDC1FFB4}"/>
-    <hyperlink ref="M19" r:id="rId53" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{1313BBEF-34BE-4488-AF92-D86AB39509B2}"/>
-    <hyperlink ref="M21" r:id="rId54" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{01ED11D7-9FF4-409B-ACF3-EE62ABA0649F}"/>
-    <hyperlink ref="M23" r:id="rId55" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{4160827D-D0A2-40F7-A68C-4B835189EF9B}"/>
-    <hyperlink ref="M25" r:id="rId56" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{2CE076BD-F288-4C2E-BE90-3BEEF265899D}"/>
-    <hyperlink ref="M27" r:id="rId57" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{C3A974BE-66FD-47CD-9D37-FA50DF4422F4}"/>
-    <hyperlink ref="M29" r:id="rId58" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{E7B0C8F4-39A1-46ED-A851-579617156F01}"/>
-    <hyperlink ref="M31" r:id="rId59" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{4729F4DE-489A-4DB8-A7FE-9D64A990DFDD}"/>
-    <hyperlink ref="M33" r:id="rId60" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{09AEDFAB-0134-402B-84CA-EB634D543186}"/>
-    <hyperlink ref="M35" r:id="rId61" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{AC737395-9BA7-45CB-A0CB-2289F298CA4C}"/>
-    <hyperlink ref="M8" r:id="rId62" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{BC231125-2970-4258-B684-31E72EDB60BB}"/>
-    <hyperlink ref="M10" r:id="rId63" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{0AC0D400-3A35-4845-8E1E-83A9C87D70C7}"/>
-    <hyperlink ref="M12" r:id="rId64" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{7E41F742-CC26-4482-8E9B-EACDFEA310D0}"/>
-    <hyperlink ref="M14" r:id="rId65" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{1C1E0808-1D39-4244-9B8E-DB5DC8C04B1F}"/>
-    <hyperlink ref="M16" r:id="rId66" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{BC5D41A4-16D3-48AF-87A6-6DDCE7A89018}"/>
-    <hyperlink ref="M18" r:id="rId67" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{19B5B32E-46D8-4BAD-92B5-1F62DABF8E7C}"/>
-    <hyperlink ref="M20" r:id="rId68" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{CA7E6EFD-A9C5-4444-A38E-D43D98AE6B3C}"/>
-    <hyperlink ref="M22" r:id="rId69" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{A8068726-9666-4F27-9B7C-340BA1A93B1E}"/>
-    <hyperlink ref="M24" r:id="rId70" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{80ADEDCD-3B13-4817-A75F-876AB59D1DF9}"/>
-    <hyperlink ref="M26" r:id="rId71" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{E07468F0-4F40-404F-853B-B147D01E1E57}"/>
-    <hyperlink ref="M28" r:id="rId72" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{35CD8011-7206-4298-959D-CDFD3ABB08B3}"/>
-    <hyperlink ref="M30" r:id="rId73" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{3A4523A2-4702-42BB-9AD4-B11C7EBE1D81}"/>
-    <hyperlink ref="M32" r:id="rId74" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{84A8A39C-3CE4-4A41-9715-6FC29AF78D86}"/>
-    <hyperlink ref="M34" r:id="rId75" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{D04E4BE9-96B2-48A1-8FDE-D40C93F0741D}"/>
-    <hyperlink ref="M3:M4" r:id="rId76" display="https://academic.oup.com/gji/article/71/3/809/656230?login=true" xr:uid="{6408A173-19E0-4D03-BA7B-A595C33041FB}"/>
-    <hyperlink ref="M37" r:id="rId77" display="https://journals.ametsoc.org/view/journals/clim/16/6/1520-0442_2003_016_0982_svatcc_2.0.co_2.xml" xr:uid="{DC46C350-4290-4180-8392-ABDB17880D3C}"/>
-    <hyperlink ref="M40:M43" r:id="rId78" display="https://link.springer.com/article/10.1007/s10236-005-0044-z" xr:uid="{9304BA43-9C4D-4327-A0EA-C0D9404AB1AE}"/>
-    <hyperlink ref="M46" r:id="rId79" display="https://journals.ametsoc.org/view/journals/phoc/36/6/jpo2876.1.xml" xr:uid="{00BA547B-96F7-43F5-AC6E-DCF63F4AC25E}"/>
-    <hyperlink ref="M48:M52" r:id="rId80" location="tocto1n3" display="https://journals.openedition.org/mediterranee/170 - tocto1n3" xr:uid="{AE4A0D0C-A23B-4700-99F5-7C3EAE2558A6}"/>
-    <hyperlink ref="M55:M58" r:id="rId81" display="https://www.sciencedirect.com/science/article/pii/S0278434309002313" xr:uid="{E4FF8234-559C-4D49-A65D-CF85C45F6E63}"/>
-    <hyperlink ref="M65" r:id="rId82" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2011JF001964" xr:uid="{C26E73A6-6BBF-442B-A9D7-3A226903E115}"/>
-    <hyperlink ref="M67:M68" r:id="rId83" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/jgrc.20377" xr:uid="{BF3EC7D0-FEE1-42FD-9DD3-E1EB29DF6CE5}"/>
-    <hyperlink ref="M71:M74" r:id="rId84" location="s0010" display="https://www.sciencedirect.com/science/article/pii/S0278434313001283 - s0010" xr:uid="{88F7743B-2CF3-4222-981F-7E66E9971F4A}"/>
-    <hyperlink ref="M76" r:id="rId85" display="https://link.springer.com/article/10.1007/s10236-013-0598-0" xr:uid="{E902FB01-F6DD-45FB-8EC7-922E37BCF8E7}"/>
-    <hyperlink ref="M78:M88" r:id="rId86" display="https://meridian.allenpress.com/jcr/article/29/6a/118/144016/Nineteenth-Century-North-American-and-Pacific" xr:uid="{70BE04C3-F47B-4A67-8FA5-A01770AFAD2E}"/>
-    <hyperlink ref="M90:M93" r:id="rId87" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/2014GL059574" xr:uid="{E560C4C4-E49D-484B-8F4F-A821AE6E8C5E}"/>
-    <hyperlink ref="M95:M96" r:id="rId88" display="https://link.springer.com/article/10.1007/s00190-014-0728-6" xr:uid="{D10091BF-B1B7-4612-A9C8-36EA4DE9C564}"/>
-    <hyperlink ref="M98:M100" r:id="rId89" display="https://www.researchgate.net/publication/273705568_Maintaining_legacy_data_Saving_Belfast_Harbour_UK_tide-gauge_data_1901-2010" xr:uid="{2805C1BE-B29A-426F-AFA0-3F7979D5C074}"/>
-    <hyperlink ref="M102" r:id="rId90" display="https://refmar.shom.fr/sites/default/files/2024-07/Reconstruction serie maregraphique Saint-Nazaire par Yann Ferret 2016.pdf" xr:uid="{A9C41B97-DE03-4C75-86C3-9FEFA55FA7F4}"/>
-    <hyperlink ref="M104" r:id="rId91" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/2016GL069494" xr:uid="{18103E0C-905B-4E38-A6E4-5F0240944777}"/>
-    <hyperlink ref="M106:M143" r:id="rId92" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{C4413F2B-33C6-43D5-A03A-B55BF2EAD207}"/>
-    <hyperlink ref="M145:M148" r:id="rId93" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2017JC013645" xr:uid="{22EC404C-72AC-44A9-9328-4A14CB094B4B}"/>
-    <hyperlink ref="M151:M156" r:id="rId94" display="https://link.springer.com/article/10.1007/s12237-018-0379-6" xr:uid="{5693ABF5-6E9C-426D-A810-2F22C9CD52A5}"/>
-    <hyperlink ref="M158:M159" r:id="rId95" location="Sec2" display="https://link.springer.com/article/10.1007/s00190-019-01238-w - Sec2" xr:uid="{D8B0C963-BF87-4FEB-80F1-F2C903EBB142}"/>
-    <hyperlink ref="M161:M162" r:id="rId96" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2019JC015277" xr:uid="{97C96E36-95C2-43D0-B4C9-98A369326D90}"/>
-    <hyperlink ref="M164:M167" r:id="rId97" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2019JC015656" xr:uid="{4454DEF3-6300-4A51-B73F-0050CC8CD1F9}"/>
-    <hyperlink ref="M169:M173" r:id="rId98" display="https://theses.hal.science/tel-02899411/" xr:uid="{D05078E6-5D69-44E8-A8B7-2EC3C4BD4EDC}"/>
-    <hyperlink ref="M175:M181" r:id="rId99" display="https://rmets.onlinelibrary.wiley.com/doi/full/10.1002/gdj3.112" xr:uid="{7D9C1AE1-FF52-45B4-8395-DFE3C26B9AB1}"/>
-    <hyperlink ref="M184:M186" r:id="rId100" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2020JC016328" xr:uid="{980F57D2-7C5A-4699-B90A-22E89F05864C}"/>
-    <hyperlink ref="M188" r:id="rId101" location="section2" display="https://os.copernicus.org/articles/17/1623/2021/ - section2" xr:uid="{DB267DF2-A940-4D15-8C2F-29E73D240910}"/>
-    <hyperlink ref="M190:M203" r:id="rId102" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{BDBF166A-60F1-4853-973C-5291EFBD2167}"/>
-    <hyperlink ref="M205" r:id="rId103" display="https://hal.science/hal-04555208v1/file/Khan2023.pdf" xr:uid="{433F0C12-B690-43F6-A4FE-E09899D867DE}"/>
-    <hyperlink ref="M208" r:id="rId104" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2024JC020908" xr:uid="{B3EF503E-80A2-4402-BBDE-9040FE69857D}"/>
-    <hyperlink ref="M211:M234" r:id="rId105" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{BF1CE461-3B84-4551-9BED-EDF762BCE6E8}"/>
-    <hyperlink ref="M239" r:id="rId106" display="https://www.zooniverse.org/projects/psmsl/uk-tides" xr:uid="{5F5E2B05-7458-433E-BF1D-FB07B9D6544B}"/>
-    <hyperlink ref="M235" r:id="rId107" display="https://hgss.copernicus.org/articles/17/1/2026/" xr:uid="{FA9A33EF-29CE-443A-8AB4-58E1AA5E65D3}"/>
-    <hyperlink ref="M236:M237" r:id="rId108" display="https://hgss.copernicus.org/articles/17/1/2026/" xr:uid="{BDB16907-1E07-441F-8C11-FAB1E34DDCC7}"/>
+    <hyperlink ref="M209" r:id="rId1" xr:uid="{3B3BC2EB-07A7-4388-8DE3-0B4BE623A44F}"/>
+    <hyperlink ref="M238" r:id="rId2" xr:uid="{76D41B0C-176D-4DCA-A7B0-148F54D438D6}"/>
+    <hyperlink ref="M189" r:id="rId3" xr:uid="{ED199385-3869-42EF-8C0C-B78D855CFBD6}"/>
+    <hyperlink ref="M207" r:id="rId4" xr:uid="{1EC0D7B3-38E6-4FC7-B9BD-8BE20F164A1C}"/>
+    <hyperlink ref="M54" r:id="rId5" xr:uid="{07E3CD6B-5FC6-4613-81A2-BE92995204E2}"/>
+    <hyperlink ref="M59" r:id="rId6" xr:uid="{31D74E63-CDB0-4403-853F-8D303ABE669E}"/>
+    <hyperlink ref="M60" r:id="rId7" xr:uid="{B8688911-0B7D-4852-B0CF-0DFBB3375335}"/>
+    <hyperlink ref="M62" r:id="rId8" xr:uid="{1ADFE9F5-747D-4123-826A-32BB24BDB434}"/>
+    <hyperlink ref="M63" r:id="rId9" xr:uid="{4C768480-6874-45BB-92EA-9286217F3F37}"/>
+    <hyperlink ref="M66" r:id="rId10" xr:uid="{3A020A2D-C1B0-4BFF-A75B-E2BA82C558E1}"/>
+    <hyperlink ref="M69" r:id="rId11" location="s0010" xr:uid="{5D4F4102-E9A8-44C3-BB8A-D949EFF93A74}"/>
+    <hyperlink ref="M89" r:id="rId12" xr:uid="{E0E660CB-C13D-47E2-8CC7-02F3466E9404}"/>
+    <hyperlink ref="M94" r:id="rId13" xr:uid="{41974C0D-C899-48E3-B8F9-A1F3596FE7C8}"/>
+    <hyperlink ref="M97" r:id="rId14" xr:uid="{026E0DB0-2AC2-4E39-818F-DFF0A4364143}"/>
+    <hyperlink ref="M157" r:id="rId15" location="Sec2" xr:uid="{3B4D3AAC-47CF-4508-9018-C84A5684680D}"/>
+    <hyperlink ref="M163" r:id="rId16" xr:uid="{6F125413-61E1-4C9B-B5C2-7CB8E424AB2D}"/>
+    <hyperlink ref="M168" r:id="rId17" xr:uid="{6F67BA82-1D7E-4810-A272-90552C4A9357}"/>
+    <hyperlink ref="M174" r:id="rId18" xr:uid="{D02339E2-CA26-404B-A61B-AB45E74ECDF4}"/>
+    <hyperlink ref="M182" r:id="rId19" xr:uid="{087F2AC3-495E-41CB-8107-0AD10D64D954}"/>
+    <hyperlink ref="M103" r:id="rId20" xr:uid="{EB67F5C1-0C5A-4FC9-863D-B122ABBD3ADE}"/>
+    <hyperlink ref="M150" r:id="rId21" xr:uid="{6E602822-A462-413C-8556-FBD612C4A3B6}"/>
+    <hyperlink ref="M70" r:id="rId22" location="s0010" xr:uid="{7CD29A62-C61A-499A-9413-7485E33AA6F4}"/>
+    <hyperlink ref="M187" r:id="rId23" location="section2" xr:uid="{1ECF59C1-51FE-416C-B411-4182A18F1416}"/>
+    <hyperlink ref="M204" r:id="rId24" xr:uid="{1A6970FE-A26E-4EA7-9AEE-2D24E9C09FD3}"/>
+    <hyperlink ref="M183" r:id="rId25" xr:uid="{FA6BC1BC-4762-4794-9633-B5608B70ADD3}"/>
+    <hyperlink ref="M105" r:id="rId26" xr:uid="{B808C8C8-0DCC-4FCA-96E6-921E91B8BECB}"/>
+    <hyperlink ref="M45" r:id="rId27" xr:uid="{348972A7-D69E-41EA-B213-F21ABAD15781}"/>
+    <hyperlink ref="M38" r:id="rId28" xr:uid="{65041048-45D4-4A88-8A43-B70DDDE6FEA4}"/>
+    <hyperlink ref="M75" r:id="rId29" xr:uid="{9D755DE4-521D-4B8D-9C65-0427B55C8416}"/>
+    <hyperlink ref="M2" r:id="rId30" xr:uid="{F25384DA-537D-4664-827D-260498FC7D86}"/>
+    <hyperlink ref="M77" r:id="rId31" xr:uid="{2016EA30-A594-4407-8F5F-279AEDDADE01}"/>
+    <hyperlink ref="M5" r:id="rId32" xr:uid="{F03F33AB-5737-44E5-A79E-5DE5AD20FBBF}"/>
+    <hyperlink ref="M47" r:id="rId33" location="tocto1n3" xr:uid="{3B721DAD-78FD-4AA2-8682-8B4B59E79EBC}"/>
+    <hyperlink ref="M206" r:id="rId34" xr:uid="{7CF77CDA-0932-47C2-8F01-5A69B8E9B95B}"/>
+    <hyperlink ref="M64" r:id="rId35" xr:uid="{B49BB6E5-677B-453E-A173-704444C8F1CE}"/>
+    <hyperlink ref="M53" r:id="rId36" location="sec2" xr:uid="{51823FDB-4EC1-4D30-AB2C-45AF9D37C653}"/>
+    <hyperlink ref="M61" r:id="rId37" xr:uid="{C303579C-BF46-444C-B4B4-DE4965DD1413}"/>
+    <hyperlink ref="M101" r:id="rId38" xr:uid="{F718EBEC-AFF1-4288-85FD-09F2ACC52B61}"/>
+    <hyperlink ref="M160" r:id="rId39" xr:uid="{427A19E3-8871-462D-B2ED-4EDE1648EF46}"/>
+    <hyperlink ref="M210" r:id="rId40" xr:uid="{9C3A377D-F241-4EF5-A93C-F5BBC0124F88}"/>
+    <hyperlink ref="M44" r:id="rId41" xr:uid="{9D9BD6F8-E0D2-4BDC-BE5A-DC3A2829BCE9}"/>
+    <hyperlink ref="M46" r:id="rId42" xr:uid="{00BA547B-96F7-43F5-AC6E-DCF63F4AC25E}"/>
+    <hyperlink ref="M158:M159" r:id="rId43" location="Sec2" display="https://link.springer.com/article/10.1007/s00190-019-01238-w - Sec2" xr:uid="{D8B0C963-BF87-4FEB-80F1-F2C903EBB142}"/>
+    <hyperlink ref="M205" r:id="rId44" xr:uid="{433F0C12-B690-43F6-A4FE-E09899D867DE}"/>
+    <hyperlink ref="M208" r:id="rId45" xr:uid="{B3EF503E-80A2-4402-BBDE-9040FE69857D}"/>
+    <hyperlink ref="M239" r:id="rId46" xr:uid="{5F5E2B05-7458-433E-BF1D-FB07B9D6544B}"/>
+    <hyperlink ref="M235" r:id="rId47" xr:uid="{FA9A33EF-29CE-443A-8AB4-58E1AA5E65D3}"/>
+    <hyperlink ref="M6:M35" r:id="rId48" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{24BD7411-EFBB-46B7-BADD-723A29361D1B}"/>
+    <hyperlink ref="M37" r:id="rId49" xr:uid="{3D967C62-5007-4F28-9DE3-61EAA9164C70}"/>
+    <hyperlink ref="M36" r:id="rId50" xr:uid="{653C2DD7-1142-4ED7-B594-2088ADA1959A}"/>
+    <hyperlink ref="M3:M4" r:id="rId51" display="https://academic.oup.com/gji/article/71/3/809/656230?login=true" xr:uid="{3508DF27-5EC0-49F1-83CC-6E7745A67989}"/>
+    <hyperlink ref="M39" r:id="rId52" xr:uid="{FC482D97-161F-48DC-9077-5F4AD949E65E}"/>
+    <hyperlink ref="M40" r:id="rId53" xr:uid="{5AA4BEC5-8773-457C-B6B6-72231B61AA1A}"/>
+    <hyperlink ref="M41" r:id="rId54" xr:uid="{A7C577FD-0189-43FF-A9EA-83F56E3C8F86}"/>
+    <hyperlink ref="M42" r:id="rId55" xr:uid="{12CB3403-9105-41C1-A1F5-6264DDF50D45}"/>
+    <hyperlink ref="M43" r:id="rId56" xr:uid="{42ACD472-DED5-4147-9BB5-995E26C8D69B}"/>
+    <hyperlink ref="M48" r:id="rId57" location="tocto1n3" xr:uid="{CE671A36-C3CC-47A7-9DEE-42CB36A4CF65}"/>
+    <hyperlink ref="M49" r:id="rId58" location="tocto1n3" xr:uid="{B1197F3C-1E3A-46B9-89B9-955905982DC1}"/>
+    <hyperlink ref="M50" r:id="rId59" location="tocto1n3" xr:uid="{C36AFFF3-619C-4348-BC44-4FEFC0801293}"/>
+    <hyperlink ref="M51" r:id="rId60" location="tocto1n3" xr:uid="{04D735CC-A641-427D-AFC2-E08824F25EA2}"/>
+    <hyperlink ref="M52" r:id="rId61" location="tocto1n3" xr:uid="{6EBFBD99-9D28-4725-A850-643AE9312F7C}"/>
+    <hyperlink ref="M55" r:id="rId62" xr:uid="{A8856F18-DC6A-44CD-BA6E-9F4626EE040A}"/>
+    <hyperlink ref="M56" r:id="rId63" xr:uid="{DD3F2BC4-834D-4835-9AA1-3081FF746C27}"/>
+    <hyperlink ref="M57" r:id="rId64" xr:uid="{E5DFC9AD-63C8-4A5F-9585-1017B4C81BAC}"/>
+    <hyperlink ref="M58" r:id="rId65" xr:uid="{6B3D50E5-552B-461E-8896-676BA6DE0178}"/>
+    <hyperlink ref="M65" r:id="rId66" xr:uid="{F705F859-536B-44E0-A564-6A11A0237F44}"/>
+    <hyperlink ref="M67" r:id="rId67" xr:uid="{4DFDDE3D-D1EF-43E1-9398-F7F5D6BECC1F}"/>
+    <hyperlink ref="M68" r:id="rId68" xr:uid="{A4F41CDC-D22B-485B-BE43-F6024B19052D}"/>
+    <hyperlink ref="M71" r:id="rId69" location="s0010" xr:uid="{16C8CD25-794E-48F4-99E0-8945750FA9E3}"/>
+    <hyperlink ref="M72" r:id="rId70" location="s0010" xr:uid="{E9F0DAA3-6775-476B-930E-ECAD0776A468}"/>
+    <hyperlink ref="M73" r:id="rId71" location="s0010" xr:uid="{D9E9269F-02D3-4ADA-B4D3-4F2EC9BE8DB6}"/>
+    <hyperlink ref="M74" r:id="rId72" location="s0010" xr:uid="{939CD655-31E0-4013-B990-814A0AFF7EB6}"/>
+    <hyperlink ref="M76" r:id="rId73" xr:uid="{7E3509B3-4650-404A-9467-584AF65FF8EC}"/>
+    <hyperlink ref="M78" r:id="rId74" xr:uid="{321C45A2-3279-401B-AC40-83CD193BA81A}"/>
+    <hyperlink ref="M79" r:id="rId75" xr:uid="{2AE441B3-985B-4C4B-8FD5-8234EDADAD46}"/>
+    <hyperlink ref="M80" r:id="rId76" xr:uid="{E1FBA3E1-96D9-4EF4-9E68-45B9B1936408}"/>
+    <hyperlink ref="M81" r:id="rId77" xr:uid="{7DA148E3-B1BC-46A1-97BE-B71890855A0F}"/>
+    <hyperlink ref="M82:M88" r:id="rId78" display="https://www.researchgate.net/publication/261063515_Nineteenth_Century_North_American_and_Pacific_Tidal_Data_Lost_or_Just_Forgotten" xr:uid="{9D855C3B-F5F6-4063-9FA3-AB8262C62C44}"/>
+    <hyperlink ref="M90" r:id="rId79" xr:uid="{56A1208E-4C55-426C-B128-4E008A9D5B9E}"/>
+    <hyperlink ref="M91" r:id="rId80" xr:uid="{9A4FD5C5-3F6D-4EE9-B20D-D0F53080DC2B}"/>
+    <hyperlink ref="M92" r:id="rId81" xr:uid="{8E0259A8-9603-417B-A394-F6BB57F942BB}"/>
+    <hyperlink ref="M93" r:id="rId82" xr:uid="{731FDA46-2751-4315-8BBB-D47285E8D8DE}"/>
+    <hyperlink ref="M95" r:id="rId83" xr:uid="{5AFF8D29-9726-40D8-A4AD-24596A945810}"/>
+    <hyperlink ref="M96" r:id="rId84" xr:uid="{1488773A-2AB4-4FC4-BD44-481092FB2DBA}"/>
+    <hyperlink ref="M98" r:id="rId85" xr:uid="{2BC4C52D-E9DE-458E-910A-FAD910E3BBCC}"/>
+    <hyperlink ref="M99" r:id="rId86" xr:uid="{B00B0EDE-4F62-46E3-91D5-1C48FF74C4C4}"/>
+    <hyperlink ref="M100" r:id="rId87" xr:uid="{95E0287C-C0C0-4011-A540-8F5C9344D7AA}"/>
+    <hyperlink ref="M102" r:id="rId88" xr:uid="{2C0C8AD6-B492-42DD-8E0E-DD4D3866605B}"/>
+    <hyperlink ref="M104" r:id="rId89" xr:uid="{FA641985-E8B1-4113-B4AE-0921B9540C7D}"/>
+    <hyperlink ref="M106:M143" r:id="rId90" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{4D9FBFA3-D23D-41BA-AA40-4599AD13A001}"/>
+    <hyperlink ref="M144" r:id="rId91" xr:uid="{E1B4DEFC-E5C7-4A34-92A4-025E0AE3150E}"/>
+    <hyperlink ref="M145" r:id="rId92" xr:uid="{ECF88FF5-F980-422C-B477-085062C4E529}"/>
+    <hyperlink ref="M146" r:id="rId93" xr:uid="{078A76F6-58D0-4468-A858-F393F98F658D}"/>
+    <hyperlink ref="M147" r:id="rId94" xr:uid="{C8C91214-328B-49CA-ACB6-B354D6C1F606}"/>
+    <hyperlink ref="M148" r:id="rId95" xr:uid="{E49CEF9F-F567-407B-BDC4-AA080137EC7A}"/>
+    <hyperlink ref="M149" r:id="rId96" xr:uid="{C50E6AEE-D397-4750-96D8-A02810F6AF48}"/>
+    <hyperlink ref="M151" r:id="rId97" xr:uid="{131663E7-33FB-4531-93A2-6372DD6037C0}"/>
+    <hyperlink ref="M152" r:id="rId98" xr:uid="{0C256CC1-0BCD-44B0-84DF-6374F5510538}"/>
+    <hyperlink ref="M153" r:id="rId99" xr:uid="{65285280-15A2-44DB-B72F-D28C05A4E877}"/>
+    <hyperlink ref="M154" r:id="rId100" xr:uid="{ADAF3B4D-1BAC-49BF-8FD8-56418B23AB7D}"/>
+    <hyperlink ref="M155" r:id="rId101" xr:uid="{2D3EBC6C-805F-440C-9DC0-2D334A9F42BC}"/>
+    <hyperlink ref="M156" r:id="rId102" xr:uid="{999846F5-FEE8-444B-A60B-8A7B699DBC2F}"/>
+    <hyperlink ref="M158" r:id="rId103" location="Sec2" xr:uid="{F13FB530-C41D-4505-9940-238B55EDE5E0}"/>
+    <hyperlink ref="M159" r:id="rId104" location="Sec2" xr:uid="{D375F386-03C0-4475-8A88-E8BC0A9EB4C3}"/>
+    <hyperlink ref="M161" r:id="rId105" xr:uid="{A42333B2-049B-43EB-914B-28D2C7EC8CCA}"/>
+    <hyperlink ref="M162" r:id="rId106" xr:uid="{C39529F3-155B-458A-8FDB-91795A99416F}"/>
+    <hyperlink ref="M164" r:id="rId107" xr:uid="{0A1664E6-8D1E-4EA3-9FBD-79D0468A22FD}"/>
+    <hyperlink ref="M165" r:id="rId108" xr:uid="{B9BEB5A9-17DB-4C7D-A1C3-20A39229CA29}"/>
+    <hyperlink ref="M166" r:id="rId109" xr:uid="{36817F4A-CBBC-4BFC-8B3C-A93DB16D1EC7}"/>
+    <hyperlink ref="M167" r:id="rId110" xr:uid="{690E80AB-3618-4257-8D83-B47D14688F30}"/>
+    <hyperlink ref="M169" r:id="rId111" xr:uid="{64365C79-97C8-4513-B75A-C0B9B7DFAF84}"/>
+    <hyperlink ref="M170" r:id="rId112" xr:uid="{BF5516BC-9984-4396-8B86-261EA5787689}"/>
+    <hyperlink ref="M171" r:id="rId113" xr:uid="{2F2D3722-3621-4171-82DF-E93A04C075E1}"/>
+    <hyperlink ref="M172" r:id="rId114" xr:uid="{7EA6AFD3-7A8E-47E5-9264-3DA91306524C}"/>
+    <hyperlink ref="M173" r:id="rId115" xr:uid="{59E1B0B9-2782-45E6-AB5B-A79C31E66F5E}"/>
+    <hyperlink ref="M175" r:id="rId116" xr:uid="{37EF509B-5100-445C-B25C-A14849AC8B22}"/>
+    <hyperlink ref="M176" r:id="rId117" xr:uid="{11B3C1A8-FB32-43F8-9786-68351674B168}"/>
+    <hyperlink ref="M177" r:id="rId118" xr:uid="{CA07AEB5-93F0-48C1-9A7D-21955B86F509}"/>
+    <hyperlink ref="M178" r:id="rId119" xr:uid="{C205AE12-C373-4A95-AD08-DC153A7692C9}"/>
+    <hyperlink ref="M179" r:id="rId120" xr:uid="{BAA490DE-24AF-496C-A944-AFE618E89A55}"/>
+    <hyperlink ref="M180" r:id="rId121" xr:uid="{AD475A5E-E822-4E4D-9043-9F1C76A15275}"/>
+    <hyperlink ref="M181" r:id="rId122" xr:uid="{19B60015-5DD0-4881-AD1A-4E8A92834104}"/>
+    <hyperlink ref="M184" r:id="rId123" xr:uid="{4230630E-8E31-4F94-9060-84925822AC5A}"/>
+    <hyperlink ref="M185" r:id="rId124" xr:uid="{9BA68D3E-1DF8-4DCC-AB36-DB2AAE25B162}"/>
+    <hyperlink ref="M186" r:id="rId125" xr:uid="{CD3C4809-4BC9-4151-AB8B-D92FC8E283B4}"/>
+    <hyperlink ref="M188" r:id="rId126" location="section2" xr:uid="{93E8E16A-C463-4941-AC2C-5E171B2FD129}"/>
+    <hyperlink ref="M190:M203" r:id="rId127" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{07A28231-0868-47FD-B96B-3BDB695A20E3}"/>
+    <hyperlink ref="M211" r:id="rId128" xr:uid="{145EBFB4-61F2-4D70-87D6-F5B09F284D2B}"/>
+    <hyperlink ref="M212" r:id="rId129" xr:uid="{6D7EFE46-FFFB-400A-87DE-A59E1D9D437F}"/>
+    <hyperlink ref="M213" r:id="rId130" xr:uid="{9F989D22-D74E-4A69-A148-CF65FD838B94}"/>
+    <hyperlink ref="M214" r:id="rId131" xr:uid="{897E005C-A3C1-4FF3-ABCF-0E737580E87C}"/>
+    <hyperlink ref="M215" r:id="rId132" xr:uid="{4ED77876-FF1E-4F49-ADF5-85CE38C596FF}"/>
+    <hyperlink ref="M216" r:id="rId133" xr:uid="{5B0CB9BE-E81B-4ECE-A435-B956D3A7476B}"/>
+    <hyperlink ref="M217" r:id="rId134" xr:uid="{6292DE55-83A5-4273-89C4-1157BBDFBA02}"/>
+    <hyperlink ref="M218" r:id="rId135" xr:uid="{97ACE801-495E-4131-B4B3-AF42FA88EA4F}"/>
+    <hyperlink ref="M219" r:id="rId136" xr:uid="{DA39D34E-32BE-42C5-B046-79DA2F5510FE}"/>
+    <hyperlink ref="M220" r:id="rId137" xr:uid="{76EB78C9-7AD4-422D-A0EA-E53F4471B5E8}"/>
+    <hyperlink ref="M221" r:id="rId138" xr:uid="{26E96A42-A256-4FE1-85B4-44E4DF537C58}"/>
+    <hyperlink ref="M222" r:id="rId139" xr:uid="{DAFD8D19-E81E-4AFB-8573-18F47EDB7D3F}"/>
+    <hyperlink ref="M234" r:id="rId140" xr:uid="{B1E6B0E3-0DCA-469E-A992-A792EC46D0E2}"/>
+    <hyperlink ref="M233" r:id="rId141" xr:uid="{43B6A8DC-0F36-4692-A1E9-B530D333DFA4}"/>
+    <hyperlink ref="M232" r:id="rId142" xr:uid="{AEFD4F05-4463-490B-AB3F-58C18EBF172E}"/>
+    <hyperlink ref="M231" r:id="rId143" xr:uid="{010AACEC-5712-498B-B67A-CA2641C86825}"/>
+    <hyperlink ref="M230" r:id="rId144" xr:uid="{EFAE9DF6-D984-4177-9504-FA4A69E29528}"/>
+    <hyperlink ref="M229" r:id="rId145" xr:uid="{A11F3AD8-B19A-419E-80D7-E9EFBA74F8A2}"/>
+    <hyperlink ref="M228" r:id="rId146" xr:uid="{3AB79308-468B-4C3F-9C4C-D476FDF82CD3}"/>
+    <hyperlink ref="M227" r:id="rId147" xr:uid="{AE7F21BB-B64E-4478-A8DD-A923AA1E0393}"/>
+    <hyperlink ref="M226" r:id="rId148" xr:uid="{42C16ABE-4E91-4A36-83B9-F431FA525505}"/>
+    <hyperlink ref="M225" r:id="rId149" xr:uid="{F038FC53-2FEA-4A91-9623-2371AC96E279}"/>
+    <hyperlink ref="M224" r:id="rId150" xr:uid="{B989BD58-5BC7-41BC-88F0-921795AE053B}"/>
+    <hyperlink ref="M223" r:id="rId151" xr:uid="{63AD07E0-53C4-40E3-B524-609B46A32B86}"/>
+    <hyperlink ref="M236" r:id="rId152" xr:uid="{1C6977C6-EDF9-414A-ABE8-31C66EDD9BF9}"/>
+    <hyperlink ref="M237" r:id="rId153" xr:uid="{2734F33F-2D2E-4849-A0EC-22815CBDB7EC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId109"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId154"/>
 </worksheet>
 </file>